--- a/factsheets/factsheets_gamme_one_life.xlsx
+++ b/factsheets/factsheets_gamme_one_life.xlsx
@@ -1438,15 +1438,34 @@
           <t>AMUNDI ASSET MANAGEMENT</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>INTROUVABLE</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>TROUVE</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>morningstar</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>28/02/2022</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>https://doc.morningstar.com/LatestDoc.aspx?clientid=unience&amp;key=21a2546a9b5481a0&amp;language=451&amp;investmentid=F00000NMTJ&amp;documenttype=52&amp;investmenttype=1&amp;frame=0</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1456,7 +1475,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Aucun 'MonthlyFactsheet' dans l'API documents Amundi (sites lu/fr/de/es/ch/ie) ; seule une 'SubfundWeeklyFactsheet' du 22/03/2023 (très ancienne, non retenue) : https://www.amundi.lu/dl/doc/subfund-weekly-factsheet/IE00B61N8946/ENG/AMUNDI/20230322. Site metori.com sans reporting public ; Morningstar non joignable (anti-bot).</t>
+          <t>Seule factsheet trouvée : Monthly report Lyxor Epsilon Global Trend - Class A EUR au 28/02/2022 via Morningstar (SecId F00000NMTJ), ISIN présent. TRÈS ANCIENNE (&gt; 4 ans) : plus de reporting publié depuis (fonds possiblement fermé/sans distribution). La 'SubfundWeeklyFactsheet' Amundi du 22/03/2023 est en fait une note SVB/Credit Suisse, pas une fiche. fundinfo : pas de MR.</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1614,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Fonds Apicil Trésorerie GAC géré par Groupama AM (confirmé Morningstar) mais absent de la base produits publique groupama-am.com (API ProductAPI/DocumentAPI : aucun produit pour cet ISIN) ; URLs Reporting_mensuel_des_OPC_French_FR0012534840_2026-09/10-JJ.pdf testées : 404. Site apicil-am.com injoignable. Probablement fonds dédié (Apicil) sans reporting public.</t>
+          <t>Fonds Apicil Trésorerie GAC géré par Groupama AM (confirmé Morningstar) mais absent de la base produits publique groupama-am.com (API ProductAPI/DocumentAPI : aucun produit pour cet ISIN) ; URLs Reporting_mensuel_des_OPC_French_FR0012534840_2026-09/10-JJ.pdf testées : 404. Site apicil-am.com injoignable. Probablement fonds dédié (Apicil) sans reporting public. | Passe fix : fundinfo (FR/LU/DE/CH/BE-priv) sans fiche mensuelle (MR) ; Morningstar LatestDoc type 52 : 404.</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2200,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Page fonds AXA IM existe (ISIN LU2485150747 dans la page) mais documents chargés en JS (Kurtosys), non accessibles par curl; Morningstar (SecId F00001DZ9K) sans factsheet (404). Part institutionnelle BX. Gestion désormais BNP Paribas AM.</t>
+          <t>Page fonds AXA IM existe (ISIN LU2485150747 dans la page) mais documents chargés en JS (Kurtosys), non accessibles par curl; Morningstar (SecId F00001DZ9K) sans factsheet (404). Part institutionnelle BX. Gestion désormais BNP Paribas AM. | Passe fix : fundinfo (FR/LU/DE/CH/BE-priv) sans fiche mensuelle (MR) ; Morningstar LatestDoc type 52 : 404.</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3712,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>La page de la part LU1502282632 renvoie 403 (profils LU/FR/BE/IT/DE/ES/CH) : part peut-être fermée/non distribuée. Seul le rapport mensuel du compartiment au 30/09/2026 a été trouvé, mais il couvre la classe C (USD) LU1502282558 et D LU1502282715 — ISIN demandé absent.</t>
+          <t>La page de la part LU1502282632 renvoie 403 (profils LU/FR/BE/IT/DE/ES/CH) : part peut-être fermée/non distribuée. Seul le rapport mensuel du compartiment au 30/09/2026 a été trouvé, mais il couvre la classe C (USD) LU1502282558 et D LU1502282715 — ISIN demandé absent. | Passe fix : fundinfo (FR/LU/DE/CH/BE-priv) sans fiche mensuelle (MR) ; Morningstar LatestDoc type 52 : 404. fundinfo n'a qu'un commentaire mensuel du compartiment (MC, août 2026) sans la part.</t>
         </is>
       </c>
     </row>
@@ -8148,20 +8167,35 @@
           <t>EDMOND DE ROTHSCHILD ASSET MANAGEMENT LUXEMBOURG</t>
         </is>
       </c>
-      <c r="D153" s="4" t="inlineStr">
-        <is>
-          <t>INTROUVABLE</t>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>TROUVE</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>fundinfo (doc. officiel gestionnaire)</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t>https://api.fundinfo.com/document/91f65629fafca4f57fb395b319af8f1c_701313/MR_FR_en_LU1244893696_YES_2026-08-31.pdf?apiKey=b9934aa2-1a83-4286-b11b-c8415da9e581</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Site EdR AM (am.edmond-de-rothschild.com, funds.edram.com redirige) protégé par Cloudflare (403 challenge JS) et non résolu par WebFetch ; pas d'URL de factsheet directe trouvée ; agrégateur ebnbanco.com : seulement DIC/prospectus/rapports, pas de factsheet.</t>
+          <t>Factsheet officielle hébergée par fundinfo (api.fundinfo.com, clé publique b9934aa2), téléchargée : EdR Fund Big Data A-EUR, « Advertising communication as of 31 August 2026 » (EN, pas de version FR sur fundinfo) ; ISIN présent dans le PDF. Date lue : 31/08/2026 (fiche de fin août ; septembre pas encore publiée sur fundinfo).</t>
         </is>
       </c>
     </row>
@@ -8340,20 +8374,35 @@
           <t>EDMOND DE ROTHSCHILD ASSET MANAGEMENT LUXEMBOURG</t>
         </is>
       </c>
-      <c r="D157" s="4" t="inlineStr">
-        <is>
-          <t>INTROUVABLE</t>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>TROUVE</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>fundinfo (doc. officiel gestionnaire)</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I157" s="3" t="inlineStr">
+        <is>
+          <t>https://api.fundinfo.com/document/745d4c3ce90b64f518f3b0138f53f954_751858/MR_FR_fr_LU1161526576_YES_2026-08-31.pdf?apiKey=b9934aa2-1a83-4286-b11b-c8415da9e581</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>Site EdR AM (am.edmond-de-rothschild.com, funds.edram.com redirige) protégé par Cloudflare (403 challenge JS) et non résolu par WebFetch ; pas d'URL de factsheet directe trouvée ; agrégateur ebnbanco.com : seulement DIC/prospectus/rapports, pas de factsheet.</t>
+          <t>Factsheet officielle hébergée par fundinfo (api.fundinfo.com, clé publique b9934aa2), téléchargée : EdR Fund Bond Allocation R-EUR, « Document publicitaire au 31 août 2026 » ; ISIN présent dans le PDF. Date lue : 31/08/2026 (fiche de fin août ; septembre pas encore publiée sur fundinfo).</t>
         </is>
       </c>
     </row>
@@ -8373,20 +8422,35 @@
           <t>EDMOND DE ROTHSCHILD ASSET MANAGEMENT LUXEMBOURG</t>
         </is>
       </c>
-      <c r="D158" s="4" t="inlineStr">
-        <is>
-          <t>INTROUVABLE</t>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>TROUVE</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>fundinfo (doc. officiel gestionnaire)</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I158" s="3" t="inlineStr">
+        <is>
+          <t>https://api.fundinfo.com/document/f86e0fbec44f30887768301ee702253a_459447/MR_FR_fr_LU1160356009_YES_2026-08-31.pdf?apiKey=b9934aa2-1a83-4286-b11b-c8415da9e581</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Site EdR AM (am.edmond-de-rothschild.com, funds.edram.com redirige) protégé par Cloudflare (403 challenge JS) et non résolu par WebFetch ; pas d'URL de factsheet directe trouvée ; agrégateur ebnbanco.com : seulement DIC/prospectus/rapports, pas de factsheet.</t>
+          <t>Factsheet officielle hébergée par fundinfo (api.fundinfo.com, clé publique b9934aa2), téléchargée : EdR Fund Healthcare A-EUR, « Document publicitaire au 31 août 2026 » ; ISIN présent dans le PDF. Date lue : 31/08/2026 (fiche de fin août ; septembre pas encore publiée sur fundinfo).</t>
         </is>
       </c>
     </row>
@@ -16667,9 +16731,14 @@
           <t>M&amp;G Luxembourg S.A.</t>
         </is>
       </c>
-      <c r="D327" s="4" t="inlineStr">
-        <is>
-          <t>INTROUVABLE</t>
+      <c r="D327" s="5" t="inlineStr">
+        <is>
+          <t>NON_VERIFIE</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>gestionnaire</t>
         </is>
       </c>
       <c r="G327" t="inlineStr"/>
@@ -16678,9 +16747,14 @@
           <t>non</t>
         </is>
       </c>
+      <c r="I327" s="3" t="inlineStr">
+        <is>
+          <t>https://api.fundinfo.com/document/9c2bbf1ed0f324b35d74a95c03fc985c_96104/MR_LU_en_LU3149167358_YES_2026-08-31.pdf?apiKey=b9934aa2-1a83-4286-b11b-c8415da9e581</t>
+        </is>
+      </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>Aucune factsheet M&amp;G pour LU3149167358 (URL déduites en 404, recherche web sans résultat). La factsheet de la part USD S (LU1670713921, au 31/08/2026) ne liste pas cette part.</t>
+          <t>fundinfo (LU-priv) et Morningstar (SecId F00001SEXW) indexent sous cet ISIN la factsheet M&amp;G (Lux) Episode Macro Fund « EUR Class S-H – Accumulation » au 31/08/2026, mais le PDF porte l'ISIN LU1670714226 (S-H, couverte) ; LU3149167358 absent du tableau des parts. Part demandée (S EUR) non identifiée dans le document.</t>
         </is>
       </c>
     </row>
@@ -16748,20 +16822,35 @@
           <t>M&amp;G Luxembourg S.A.</t>
         </is>
       </c>
-      <c r="D329" s="4" t="inlineStr">
-        <is>
-          <t>INTROUVABLE</t>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t>TROUVE</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>fundinfo (doc. officiel gestionnaire)</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G329" t="inlineStr"/>
       <c r="H329" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I329" s="3" t="inlineStr">
+        <is>
+          <t>https://api.fundinfo.com/document/48769a6654ef8bf4aa0eb2d53ce2fc8c_122525/MR_FR_fr_LU1670713335_YES_2026-08-31.pdf?apiKey=b9934aa2-1a83-4286-b11b-c8415da9e581</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>Aucune factsheet M&amp;G (URL déduites en 404 dans 17 pays) ; fonds possiblement fermé/fusionné (seule trace : UK Reporting 2019).</t>
+          <t>Factsheet officielle hébergée par fundinfo (api.fundinfo.com, clé publique b9934aa2), téléchargée : M&amp;G (Lux) Global Credit Investment Fund (ex Global Corporate Bond Fund, renommé 29/05/2024) catégorie A-H EUR Cap., « Reporting mensuel au 31 août 2026 » ; ISIN présent dans le PDF. Date lue : 31/08/2026 (fiche de fin août ; septembre pas encore publiée sur fundinfo).</t>
         </is>
       </c>
     </row>
@@ -16895,7 +16984,7 @@
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t>Page fonds M&amp;G existe (contenu chargé en JS via Kurtosys) mais aucune factsheet trouvée (URL déduites LU/DE/FR/etc. en 404) ; part récente.</t>
+          <t>Page fonds M&amp;G existe (contenu chargé en JS via Kurtosys) mais aucune factsheet trouvée (URL déduites LU/DE/FR/etc. en 404) ; part récente. | Passe fix : fundinfo (FR/LU/DE/CH/BE-priv) sans fiche mensuelle (MR) ; Morningstar LatestDoc type 52 : 404. (SecId F0000288V3)</t>
         </is>
       </c>
     </row>
@@ -17475,15 +17564,34 @@
           <t>ETHENEA Independent Investors S.A.</t>
         </is>
       </c>
-      <c r="D344" s="4" t="inlineStr">
-        <is>
-          <t>INTROUVABLE</t>
-        </is>
-      </c>
-      <c r="G344" t="inlineStr"/>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>TROUVE</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>morningstar</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I344" s="3" t="inlineStr">
+        <is>
+          <t>https://doc.morningstar.com/LatestDoc.aspx?clientid=unience&amp;key=21a2546a9b5481a0&amp;language=451&amp;investmentid=F00001CXFD&amp;documenttype=52&amp;investmenttype=1&amp;frame=0</t>
         </is>
       </c>
       <c r="J344" s="3" t="inlineStr">
@@ -17493,7 +17601,7 @@
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>Pas de factsheet sur la page ETHENEA (seulement KID/prospectus/avis); lien factsheetslive renvoie 'document non disponible'. Avis du 02/10/2026: fonds absorbé par LAIQON SICAV - Megatrends Asia au 01/10/2026 (fusion sur VNI du 30/09/2026).</t>
+          <t>Factsheet MainFirst - Megatrends Asia (A) via Morningstar (SecId F00001CXFD), « Factsheet as of 27 February 2026 », ISIN présent. ANCIENNE (&gt; 3 mois) ; fonds absorbé par LAIQON SICAV - Megatrends Asia au 01/10/2026 (avis ETHENEA 02/10/2026). fundinfo : pas de MR.</t>
         </is>
       </c>
     </row>
@@ -18022,19 +18130,19 @@
           <t>Moneta Asset Management</t>
         </is>
       </c>
-      <c r="D355" s="5" t="inlineStr">
-        <is>
-          <t>AUTRE_SOURCE</t>
+      <c r="D355" s="2" t="inlineStr">
+        <is>
+          <t>TROUVE</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>autre</t>
+          <t>morningstar</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>28/08/2026</t>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="G355" t="inlineStr"/>
@@ -18045,7 +18153,7 @@
       </c>
       <c r="I355" s="3" t="inlineStr">
         <is>
-          <t>https://assets.finanzfluss.de/hippoverse/documents/FR0010871830-factsheet.pdf</t>
+          <t>https://doc.morningstar.com/LatestDoc.aspx?clientid=unience&amp;key=21a2546a9b5481a0&amp;language=451&amp;investmentid=F00000H177&amp;documenttype=52&amp;investmenttype=1&amp;frame=0</t>
         </is>
       </c>
       <c r="J355" s="3" t="inlineStr">
@@ -18055,7 +18163,7 @@
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t>Lettre mensuelle EN Moneta (Part R, ISIN présent) 'as of 28 August 2026', hébergée par finanzfluss. Site Moneta : bibliothèque derrière un login profil (TYPO3) non contournable en curl.</t>
+          <t>Monthly report Moneta Long Short (EN) via Morningstar (SecId F00000H177) : « MLS Part R vs indices as of 30 September 2026 », ISIN FR0010871830 (Share R) présent. Remplace la lettre d'août hébergée par finanzfluss. fundinfo : pas de MR.</t>
         </is>
       </c>
     </row>
@@ -18340,20 +18448,35 @@
           <t>Nordea Investment Funds S.A.</t>
         </is>
       </c>
-      <c r="D361" s="4" t="inlineStr">
-        <is>
-          <t>INTROUVABLE</t>
+      <c r="D361" s="2" t="inlineStr">
+        <is>
+          <t>TROUVE</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>fundinfo (doc. officiel gestionnaire)</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G361" t="inlineStr"/>
       <c r="H361" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I361" s="3" t="inlineStr">
+        <is>
+          <t>https://api.fundinfo.com/document/da366e9fbdf0842ce29a047d7cd814cf_568176/MR_FR_en_LU0445386369_YES_2026-08-31.pdf?apiKey=b9934aa2-1a83-4286-b11b-c8415da9e581</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>Site Nordea (nordea.lu) : pages fonds et documents servis dynamiquement par l'API Kurtosys (jeton requis, HTTP 401) ; noms de fichiers non devinables via /documents/ ; Morningstar bloqué (challenge anti-bot). Aucune factsheet téléchargée/vérifiée ; sources tierces (Standard Life, Finect) mentionnent des factsheets 2026 sans PDF officiel vérifié.</t>
+          <t>Factsheet officielle hébergée par fundinfo (api.fundinfo.com, clé publique b9934aa2), téléchargée : Nordea 1 - Alpha 10 MA Fund (BP-EUR), « Fact Sheet | Aug 2026 » (EN) ; ISIN présent dans le PDF. Date lue : août 2026, fichier daté 2026-08-31 (fiche de fin août ; septembre pas encore publiée sur fundinfo).</t>
         </is>
       </c>
     </row>
@@ -18373,20 +18496,35 @@
           <t>Nordea Investment Funds S.A.</t>
         </is>
       </c>
-      <c r="D362" s="4" t="inlineStr">
-        <is>
-          <t>INTROUVABLE</t>
+      <c r="D362" s="2" t="inlineStr">
+        <is>
+          <t>TROUVE</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>fundinfo (doc. officiel gestionnaire)</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G362" t="inlineStr"/>
       <c r="H362" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I362" s="3" t="inlineStr">
+        <is>
+          <t>https://api.fundinfo.com/document/e09d53ccd274e17c8c82bbc6bbf61d7a_710092/MR_FR_en_LU0602539602_YES_2026-08-31.pdf?apiKey=b9934aa2-1a83-4286-b11b-c8415da9e581</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>Site Nordea (nordea.lu) : pages fonds et documents servis dynamiquement par l'API Kurtosys (jeton requis, HTTP 401) ; noms de fichiers non devinables via /documents/ ; Morningstar bloqué (challenge anti-bot). Aucune factsheet téléchargée/vérifiée ; sources tierces (Standard Life, Finect) mentionnent des factsheets 2026 sans PDF officiel vérifié.</t>
+          <t>Factsheet officielle hébergée par fundinfo (api.fundinfo.com, clé publique b9934aa2), téléchargée : Nordea 1 - Emerging Sustainable Stars Equity Fund (BP-USD), « Fact Sheet | Aug 2026 » (EN) — fonds renommé ; ISIN présent dans le PDF. Date lue : août 2026, fichier daté 2026-08-31 (fiche de fin août ; septembre pas encore publiée sur fundinfo).</t>
         </is>
       </c>
     </row>
@@ -18406,20 +18544,35 @@
           <t>Nordea Investment Funds S.A.</t>
         </is>
       </c>
-      <c r="D363" s="4" t="inlineStr">
-        <is>
-          <t>INTROUVABLE</t>
+      <c r="D363" s="2" t="inlineStr">
+        <is>
+          <t>TROUVE</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>fundinfo (doc. officiel gestionnaire)</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G363" t="inlineStr"/>
       <c r="H363" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I363" s="3" t="inlineStr">
+        <is>
+          <t>https://api.fundinfo.com/document/8430aeeebedfee4a62359930fc05b5cd_694100/MR_FR_fr_LU0348926287_YES_2026-08-31.pdf?apiKey=b9934aa2-1a83-4286-b11b-c8415da9e581</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t>Site Nordea (nordea.lu) : pages fonds et documents servis dynamiquement par l'API Kurtosys (jeton requis, HTTP 401) ; noms de fichiers non devinables via /documents/ ; Morningstar bloqué (challenge anti-bot). Aucune factsheet téléchargée/vérifiée ; sources tierces (Standard Life, Finect) mentionnent des factsheets 2026 sans PDF officiel vérifié.</t>
+          <t>Factsheet officielle hébergée par fundinfo (api.fundinfo.com, clé publique b9934aa2), téléchargée : Nordea 1 - Global Climate and Environment Fund (BP-EUR), « Fact Sheet | août 2026 » ; ISIN présent dans le PDF. Date lue : août 2026, fichier daté 2026-08-31 (fiche de fin août ; septembre pas encore publiée sur fundinfo).</t>
         </is>
       </c>
     </row>
@@ -18439,20 +18592,35 @@
           <t>Nordea Investment Funds S.A.</t>
         </is>
       </c>
-      <c r="D364" s="4" t="inlineStr">
-        <is>
-          <t>INTROUVABLE</t>
+      <c r="D364" s="2" t="inlineStr">
+        <is>
+          <t>TROUVE</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>fundinfo (doc. officiel gestionnaire)</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G364" t="inlineStr"/>
       <c r="H364" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I364" s="3" t="inlineStr">
+        <is>
+          <t>https://api.fundinfo.com/document/f008b33dcb5ebe646f21a71e3782f96e_641498/MR_FR_fr_LU2463526074_YES_2026-08-31.pdf?apiKey=b9934aa2-1a83-4286-b11b-c8415da9e581</t>
         </is>
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t>Site Nordea (nordea.lu) : pages fonds et documents servis dynamiquement par l'API Kurtosys (jeton requis, HTTP 401) ; noms de fichiers non devinables via /documents/ ; Morningstar bloqué (challenge anti-bot). Aucune factsheet téléchargée/vérifiée ; sources tierces (Standard Life, Finect) mentionnent des factsheets 2026 sans PDF officiel vérifié.</t>
+          <t>Factsheet officielle hébergée par fundinfo (api.fundinfo.com, clé publique b9934aa2), téléchargée : Nordea 1 - Global Climate Transition Engagement Fund (BP-USD), « Fact Sheet | août 2026 » — fonds renommé ; ISIN présent dans le PDF. Date lue : août 2026, fichier daté 2026-08-31 (fiche de fin août ; septembre pas encore publiée sur fundinfo).</t>
         </is>
       </c>
     </row>
@@ -18472,20 +18640,35 @@
           <t>Nordea Investment Funds S.A.</t>
         </is>
       </c>
-      <c r="D365" s="4" t="inlineStr">
-        <is>
-          <t>INTROUVABLE</t>
+      <c r="D365" s="2" t="inlineStr">
+        <is>
+          <t>TROUVE</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>fundinfo (doc. officiel gestionnaire)</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G365" t="inlineStr"/>
       <c r="H365" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I365" s="3" t="inlineStr">
+        <is>
+          <t>https://api.fundinfo.com/document/a05ab346c83dc980279d8068db577ace_548400/MR_FR_fr_LU0078812822_YES_2026-08-31.pdf?apiKey=b9934aa2-1a83-4286-b11b-c8415da9e581</t>
         </is>
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>Site Nordea (nordea.lu) : pages fonds et documents servis dynamiquement par l'API Kurtosys (jeton requis, HTTP 401) ; noms de fichiers non devinables via /documents/ ; Morningstar bloqué (challenge anti-bot). Aucune factsheet téléchargée/vérifiée ; sources tierces (Standard Life, Finect) mentionnent des factsheets 2026 sans PDF officiel vérifié.</t>
+          <t>Factsheet officielle hébergée par fundinfo (api.fundinfo.com, clé publique b9934aa2), téléchargée : Nordea 1 - Norwegian Short-Term Bond Fund (BP-NOK), « Fact Sheet | août 2026 » ; ISIN présent dans le PDF. Date lue : août 2026, fichier daté 2026-08-31 (fiche de fin août ; septembre pas encore publiée sur fundinfo).</t>
         </is>
       </c>
     </row>
@@ -18505,15 +18688,30 @@
           <t>Nordea Investment Funds S.A.</t>
         </is>
       </c>
-      <c r="D366" s="4" t="inlineStr">
-        <is>
-          <t>INTROUVABLE</t>
+      <c r="D366" s="2" t="inlineStr">
+        <is>
+          <t>TROUVE</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>fundinfo (doc. officiel gestionnaire)</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G366" t="inlineStr"/>
       <c r="H366" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I366" s="3" t="inlineStr">
+        <is>
+          <t>https://api.fundinfo.com/document/2308c7c95381fbe3759b2984e263e4d6_851617/MR_FR_en_LU0227384020_YES_2026-08-31.pdf?apiKey=b9934aa2-1a83-4286-b11b-c8415da9e581</t>
         </is>
       </c>
       <c r="J366" s="3" t="inlineStr">
@@ -18523,7 +18721,7 @@
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>Site Nordea (nordea.lu) : pages fonds et documents servis dynamiquement par l'API Kurtosys (jeton requis, HTTP 401) ; noms de fichiers non devinables via /documents/ ; Morningstar bloqué (challenge anti-bot). Aucune factsheet téléchargée/vérifiée ; sources tierces (Standard Life, Finect) mentionnent des factsheets 2026 sans PDF officiel vérifié.</t>
+          <t>Factsheet officielle hébergée par fundinfo (api.fundinfo.com, clé publique b9934aa2), téléchargée : Nordea 1 - Stable Return Fund (BP-EUR), « Fact Sheet | Aug 2026 » (EN) ; ISIN présent dans le PDF. Date lue : août 2026, fichier daté 2026-08-31 (fiche de fin août ; septembre pas encore publiée sur fundinfo).</t>
         </is>
       </c>
     </row>
@@ -18543,15 +18741,30 @@
           <t>Nordea Investment Funds S.A.</t>
         </is>
       </c>
-      <c r="D367" s="4" t="inlineStr">
-        <is>
-          <t>INTROUVABLE</t>
+      <c r="D367" s="2" t="inlineStr">
+        <is>
+          <t>TROUVE</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>fundinfo (doc. officiel gestionnaire)</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G367" t="inlineStr"/>
       <c r="H367" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I367" s="3" t="inlineStr">
+        <is>
+          <t>https://api.fundinfo.com/document/52b8bc804ccaeb43d11e7cec840432af_513583/MR_FR_en_LU3076185084_YES_2026-08-31.pdf?apiKey=b9934aa2-1a83-4286-b11b-c8415da9e581</t>
         </is>
       </c>
       <c r="J367" s="3" t="inlineStr">
@@ -18561,7 +18774,7 @@
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>Site Nordea (nordea.lu) : pages fonds et documents servis dynamiquement par l'API Kurtosys (jeton requis, HTTP 401) ; noms de fichiers non devinables via /documents/ ; Morningstar bloqué (challenge anti-bot). Aucune factsheet téléchargée/vérifiée ; sources tierces (Standard Life, Finect) mentionnent des factsheets 2026 sans PDF officiel vérifié.</t>
+          <t>Factsheet officielle hébergée par fundinfo (api.fundinfo.com, clé publique b9934aa2), téléchargée : Nordea 1 - Empower Europe Fund (BP-EUR), « Fact Sheet | Aug 2026 » (EN) ; ISIN présent dans le PDF. Date lue : août 2026, fichier daté 2026-08-31 (fiche de fin août ; septembre pas encore publiée sur fundinfo).</t>
         </is>
       </c>
     </row>
@@ -18581,15 +18794,30 @@
           <t>Nordea Investment Funds S.A.</t>
         </is>
       </c>
-      <c r="D368" s="4" t="inlineStr">
-        <is>
-          <t>INTROUVABLE</t>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>TROUVE</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>fundinfo (doc. officiel gestionnaire)</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G368" t="inlineStr"/>
       <c r="H368" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I368" s="3" t="inlineStr">
+        <is>
+          <t>https://api.fundinfo.com/document/ca30b0e33d80df59e8428ebeb19e0031_647659/MR_FR_fr_LU0112467450_YES_2026-08-31.pdf?apiKey=b9934aa2-1a83-4286-b11b-c8415da9e581</t>
         </is>
       </c>
       <c r="J368" s="3" t="inlineStr">
@@ -18599,7 +18827,7 @@
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t>Site Nordea (nordea.lu) : pages fonds et documents servis dynamiquement par l'API Kurtosys (jeton requis, HTTP 401) ; noms de fichiers non devinables via /documents/ ; Morningstar bloqué (challenge anti-bot). Aucune factsheet téléchargée/vérifiée ; sources tierces (Standard Life, Finect) mentionnent des factsheets 2026 sans PDF officiel vérifié.</t>
+          <t>Factsheet officielle hébergée par fundinfo (api.fundinfo.com, clé publique b9934aa2), téléchargée : Nordea 1 - Global Stable Equity Fund (BP-EUR), « Fact Sheet | août 2026 » ; ISIN présent dans le PDF. Date lue : août 2026, fichier daté 2026-08-31 (fiche de fin août ; septembre pas encore publiée sur fundinfo).</t>
         </is>
       </c>
     </row>
@@ -21903,7 +22131,7 @@
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t>Roche-Brune AM absorbée par APICIL AM (fonds renommés en 2025) ; anciens domaines roche-brune.com injoignables ; site APICIL AM bloqué par Cloudflare (403) ; aucun reporting mensuel trouvé via recherche.</t>
+          <t>Roche-Brune AM absorbée par APICIL AM (fonds renommés en 2025) ; anciens domaines roche-brune.com injoignables ; site APICIL AM bloqué par Cloudflare (403) ; aucun reporting mensuel trouvé via recherche. | Passe fix : fundinfo (FR/LU/DE/CH/BE-priv) sans fiche mensuelle (MR) ; Morningstar LatestDoc type 52 : 404.</t>
         </is>
       </c>
     </row>
@@ -22770,7 +22998,7 @@
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t>Site APICIL AM (apicil-asset-management.com) entièrement derrière un challenge Cloudflare (403, y compris sitemaps/uploads) ; aucune URL de reporting mensuel trouvée via recherche ; agrégateurs (epargnoo) : seulement le DIC.</t>
+          <t>Site APICIL AM (apicil-asset-management.com) entièrement derrière un challenge Cloudflare (403, y compris sitemaps/uploads) ; aucune URL de reporting mensuel trouvée via recherche ; agrégateurs (epargnoo) : seulement le DIC. | Passe fix : fundinfo (FR/LU/DE/CH/BE-priv) sans fiche mensuelle (MR) ; Morningstar LatestDoc type 52 : 404.</t>
         </is>
       </c>
     </row>
@@ -22803,7 +23031,7 @@
       </c>
       <c r="K453" t="inlineStr">
         <is>
-          <t>Site APICIL AM (apicil-asset-management.com) entièrement derrière un challenge Cloudflare (403, y compris sitemaps/uploads) ; aucune URL de reporting mensuel trouvée via recherche ; agrégateurs (epargnoo) : seulement le DIC.</t>
+          <t>Site APICIL AM (apicil-asset-management.com) entièrement derrière un challenge Cloudflare (403, y compris sitemaps/uploads) ; aucune URL de reporting mensuel trouvée via recherche ; agrégateurs (epargnoo) : seulement le DIC. | Passe fix : fundinfo (FR/LU/DE/CH/BE-priv) sans fiche mensuelle (MR) ; Morningstar LatestDoc type 52 : 404.</t>
         </is>
       </c>
     </row>
@@ -23048,7 +23276,7 @@
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t>Aucun site gestionnaire joignable (treasurycapital.ie / tcfundsolutions.com : échec de connexion) ; recherche web : uniquement agrégateurs (finanzen.ch/.at, part C EUR Acc, administrateur Gateway Fund Services). Morningstar SecId F000010EJL trouvé mais pages Morningstar bloquées (anti-bot) ; Finect n'a pas de document.</t>
+          <t>Aucun site gestionnaire joignable (treasurycapital.ie / tcfundsolutions.com : échec de connexion) ; recherche web : uniquement agrégateurs (finanzen.ch/.at, part C EUR Acc, administrateur Gateway Fund Services). Morningstar SecId F000010EJL trouvé mais pages Morningstar bloquées (anti-bot) ; Finect n'a pas de document. | Passe fix : fundinfo (FR/LU/DE/CH/BE-priv) sans fiche mensuelle (MR) ; Morningstar LatestDoc type 52 : 404.</t>
         </is>
       </c>
     </row>
@@ -24279,7 +24507,7 @@
       </c>
       <c r="K482" t="inlineStr">
         <is>
-          <t>Waterloo Global Flexible R EUR (Waterloo Sicav, gérant Waterloo AM). Section SICAVs du site waterloo-am.com protégée par mot de passe ; fundinfo ne publie que prospectus (2024) et rapport semestriel (30/06/2024), aucune fiche mensuelle ; WebSearch sans résultat. Site Altum injoignable.</t>
+          <t>Waterloo Global Flexible R EUR (Waterloo Sicav, gérant Waterloo AM). Section SICAVs du site waterloo-am.com protégée par mot de passe ; fundinfo ne publie que prospectus (2024) et rapport semestriel (30/06/2024), aucune fiche mensuelle ; WebSearch sans résultat. Site Altum injoignable. | Passe fix : fundinfo (FR/LU/DE/CH/BE-priv) sans fiche mensuelle (MR) ; Morningstar LatestDoc type 52 : 404. (SecId F00000XYNC)</t>
         </is>
       </c>
     </row>
@@ -24372,704 +24600,719 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J69" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId128"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J92" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J94" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J97" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J99" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J100" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J101" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J103" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J104" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J105" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J106" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J107" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J108" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J109" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J111" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J116" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I119" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J127" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I128" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J128" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I129" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J129" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I130" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J130" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I131" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J131" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J132" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J133" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I134" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J134" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I135" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J135" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I137" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J137" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I138" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J138" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J139" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I140" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J140" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I141" r:id="rId221"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId222"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId223"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId224"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I145" r:id="rId225"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J146" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J147" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I148" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I154" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J154" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J155" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I156" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J156" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I160" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J160" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J161" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J162" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I163" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J163" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I164" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J164" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I165" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J165" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I166" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J166" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J167" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J168" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I170" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J170" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I171" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J171" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I172" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J172" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I173" r:id="rId266"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J173" r:id="rId267"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I174" r:id="rId268"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J174" r:id="rId269"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I175" r:id="rId270"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J175" r:id="rId271"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I176" r:id="rId272"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J176" r:id="rId273"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J193" r:id="rId274"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I199" r:id="rId275"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I200" r:id="rId276"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I201" r:id="rId277"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I202" r:id="rId278"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I203" r:id="rId279"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I204" r:id="rId280"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I205" r:id="rId281"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I206" r:id="rId282"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I207" r:id="rId283"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I208" r:id="rId284"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I209" r:id="rId285"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I210" r:id="rId286"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I211" r:id="rId287"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I212" r:id="rId288"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I213" r:id="rId289"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I214" r:id="rId290"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I215" r:id="rId291"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I216" r:id="rId292"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I217" r:id="rId293"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I218" r:id="rId294"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I219" r:id="rId295"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J219" r:id="rId296"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I220" r:id="rId297"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J220" r:id="rId298"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I221" r:id="rId299"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J221" r:id="rId300"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I222" r:id="rId301"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J222" r:id="rId302"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I223" r:id="rId303"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J223" r:id="rId304"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I224" r:id="rId305"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J224" r:id="rId306"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I225" r:id="rId307"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J225" r:id="rId308"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I226" r:id="rId309"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J226" r:id="rId310"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I227" r:id="rId311"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J227" r:id="rId312"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I228" r:id="rId313"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J228" r:id="rId314"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I229" r:id="rId315"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J229" r:id="rId316"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I230" r:id="rId317"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J230" r:id="rId318"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I231" r:id="rId319"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J231" r:id="rId320"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I232" r:id="rId321"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J232" r:id="rId322"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I233" r:id="rId323"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J233" r:id="rId324"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I234" r:id="rId325"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J234" r:id="rId326"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I235" r:id="rId327"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J235" r:id="rId328"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I236" r:id="rId329"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J236" r:id="rId330"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I237" r:id="rId331"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J237" r:id="rId332"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I238" r:id="rId333"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I239" r:id="rId334"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I240" r:id="rId335"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J240" r:id="rId336"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I241" r:id="rId337"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J241" r:id="rId338"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I242" r:id="rId339"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J242" r:id="rId340"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I243" r:id="rId341"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J243" r:id="rId342"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I244" r:id="rId343"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J244" r:id="rId344"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I245" r:id="rId345"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J245" r:id="rId346"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I246" r:id="rId347"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J246" r:id="rId348"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I247" r:id="rId349"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J247" r:id="rId350"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I248" r:id="rId351"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J248" r:id="rId352"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I249" r:id="rId353"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J249" r:id="rId354"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I250" r:id="rId355"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J250" r:id="rId356"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I251" r:id="rId357"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J251" r:id="rId358"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I252" r:id="rId359"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J252" r:id="rId360"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I253" r:id="rId361"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J253" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I254" r:id="rId363"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J254" r:id="rId364"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I255" r:id="rId365"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J255" r:id="rId366"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I256" r:id="rId367"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J256" r:id="rId368"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I257" r:id="rId369"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J257" r:id="rId370"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I258" r:id="rId371"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J258" r:id="rId372"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I259" r:id="rId373"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J259" r:id="rId374"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J260" r:id="rId375"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I261" r:id="rId376"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J261" r:id="rId377"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I262" r:id="rId378"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J262" r:id="rId379"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I263" r:id="rId380"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J263" r:id="rId381"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I264" r:id="rId382"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J264" r:id="rId383"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I265" r:id="rId384"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I266" r:id="rId385"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I267" r:id="rId386"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J267" r:id="rId387"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I268" r:id="rId388"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I269" r:id="rId389"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J269" r:id="rId390"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I270" r:id="rId391"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J270" r:id="rId392"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I271" r:id="rId393"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J271" r:id="rId394"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I272" r:id="rId395"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J272" r:id="rId396"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I273" r:id="rId397"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J273" r:id="rId398"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I274" r:id="rId399"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I275" r:id="rId400"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J275" r:id="rId401"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I276" r:id="rId402"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J276" r:id="rId403"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I277" r:id="rId404"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I278" r:id="rId405"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I279" r:id="rId406"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I280" r:id="rId407"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I281" r:id="rId408"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I282" r:id="rId409"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I283" r:id="rId410"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I284" r:id="rId411"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J284" r:id="rId412"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I285" r:id="rId413"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J285" r:id="rId414"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I286" r:id="rId415"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J286" r:id="rId416"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I287" r:id="rId417"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J287" r:id="rId418"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I288" r:id="rId419"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J288" r:id="rId420"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I289" r:id="rId421"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J289" r:id="rId422"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I290" r:id="rId423"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J290" r:id="rId424"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I291" r:id="rId425"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J291" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I292" r:id="rId427"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J292" r:id="rId428"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I293" r:id="rId429"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J293" r:id="rId430"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I294" r:id="rId431"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J294" r:id="rId432"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I295" r:id="rId433"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J295" r:id="rId434"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I296" r:id="rId435"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J296" r:id="rId436"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I297" r:id="rId437"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J297" r:id="rId438"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I298" r:id="rId439"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J298" r:id="rId440"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I299" r:id="rId441"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J299" r:id="rId442"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I300" r:id="rId443"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J300" r:id="rId444"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I301" r:id="rId445"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J301" r:id="rId446"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I302" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J302" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I303" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J303" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I304" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J304" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I305" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J305" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I306" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J306" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I307" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J307" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I308" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J308" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I309" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J309" r:id="rId462"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I310" r:id="rId463"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J310" r:id="rId464"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I311" r:id="rId465"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J311" r:id="rId466"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I312" r:id="rId467"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J312" r:id="rId468"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I313" r:id="rId469"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J313" r:id="rId470"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I314" r:id="rId471"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J314" r:id="rId472"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I315" r:id="rId473"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J315" r:id="rId474"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I316" r:id="rId475"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J316" r:id="rId476"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I317" r:id="rId477"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J317" r:id="rId478"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I318" r:id="rId479"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J318" r:id="rId480"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I319" r:id="rId481"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J319" r:id="rId482"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I320" r:id="rId483"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J320" r:id="rId484"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I321" r:id="rId485"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J321" r:id="rId486"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I322" r:id="rId487"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J322" r:id="rId488"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I323" r:id="rId489"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J323" r:id="rId490"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I324" r:id="rId491"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I325" r:id="rId492"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I326" r:id="rId493"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I328" r:id="rId494"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I330" r:id="rId495"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I331" r:id="rId496"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J332" r:id="rId497"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I333" r:id="rId498"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I334" r:id="rId499"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I335" r:id="rId500"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I336" r:id="rId501"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I337" r:id="rId502"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I338" r:id="rId503"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I339" r:id="rId504"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I340" r:id="rId505"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J340" r:id="rId506"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I341" r:id="rId507"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J341" r:id="rId508"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I342" r:id="rId509"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J342" r:id="rId510"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I343" r:id="rId511"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J343" r:id="rId512"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J344" r:id="rId513"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I345" r:id="rId514"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J345" r:id="rId515"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I346" r:id="rId516"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J346" r:id="rId517"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I347" r:id="rId518"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J347" r:id="rId519"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I348" r:id="rId520"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J348" r:id="rId521"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I349" r:id="rId522"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I350" r:id="rId523"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J350" r:id="rId524"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I351" r:id="rId525"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J351" r:id="rId526"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I352" r:id="rId527"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J352" r:id="rId528"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I354" r:id="rId529"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J354" r:id="rId530"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I355" r:id="rId531"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J355" r:id="rId532"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I356" r:id="rId533"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J356" r:id="rId534"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I357" r:id="rId535"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J357" r:id="rId536"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I358" r:id="rId537"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J358" r:id="rId538"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I359" r:id="rId539"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J359" r:id="rId540"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I360" r:id="rId541"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J360" r:id="rId542"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J366" r:id="rId543"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J367" r:id="rId544"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J368" r:id="rId545"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I369" r:id="rId546"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J369" r:id="rId547"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I370" r:id="rId548"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J370" r:id="rId549"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I371" r:id="rId550"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J371" r:id="rId551"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I372" r:id="rId552"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J372" r:id="rId553"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I373" r:id="rId554"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J373" r:id="rId555"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I374" r:id="rId556"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J374" r:id="rId557"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I375" r:id="rId558"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J375" r:id="rId559"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I376" r:id="rId560"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J376" r:id="rId561"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I377" r:id="rId562"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J377" r:id="rId563"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I378" r:id="rId564"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J378" r:id="rId565"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I379" r:id="rId566"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J379" r:id="rId567"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I380" r:id="rId568"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J380" r:id="rId569"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I381" r:id="rId570"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J381" r:id="rId571"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I382" r:id="rId572"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J382" r:id="rId573"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I383" r:id="rId574"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J383" r:id="rId575"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I384" r:id="rId576"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J384" r:id="rId577"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I385" r:id="rId578"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J385" r:id="rId579"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I386" r:id="rId580"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J386" r:id="rId581"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J387" r:id="rId582"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J388" r:id="rId583"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I389" r:id="rId584"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J389" r:id="rId585"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I390" r:id="rId586"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J390" r:id="rId587"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I391" r:id="rId588"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J391" r:id="rId589"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I392" r:id="rId590"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J392" r:id="rId591"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I393" r:id="rId592"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I394" r:id="rId593"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I395" r:id="rId594"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I396" r:id="rId595"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I397" r:id="rId596"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I398" r:id="rId597"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I399" r:id="rId598"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I400" r:id="rId599"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I401" r:id="rId600"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I402" r:id="rId601"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I403" r:id="rId602"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I404" r:id="rId603"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J404" r:id="rId604"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I405" r:id="rId605"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I406" r:id="rId606"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I407" r:id="rId607"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I408" r:id="rId608"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I409" r:id="rId609"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J409" r:id="rId610"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I410" r:id="rId611"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J410" r:id="rId612"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I411" r:id="rId613"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J411" r:id="rId614"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I412" r:id="rId615"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J412" r:id="rId616"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I413" r:id="rId617"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J413" r:id="rId618"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I415" r:id="rId619"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J415" r:id="rId620"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I416" r:id="rId621"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J416" r:id="rId622"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I417" r:id="rId623"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J417" r:id="rId624"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I418" r:id="rId625"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J418" r:id="rId626"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I419" r:id="rId627"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J419" r:id="rId628"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I420" r:id="rId629"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J420" r:id="rId630"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I421" r:id="rId631"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J421" r:id="rId632"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I422" r:id="rId633"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J422" r:id="rId634"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I423" r:id="rId635"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J423" r:id="rId636"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I424" r:id="rId637"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J424" r:id="rId638"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I425" r:id="rId639"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J425" r:id="rId640"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I426" r:id="rId641"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J426" r:id="rId642"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I427" r:id="rId643"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J427" r:id="rId644"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I428" r:id="rId645"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J428" r:id="rId646"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I429" r:id="rId647"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J429" r:id="rId648"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I430" r:id="rId649"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J430" r:id="rId650"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I431" r:id="rId651"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J431" r:id="rId652"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I432" r:id="rId653"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J432" r:id="rId654"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I434" r:id="rId655"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J434" r:id="rId656"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I435" r:id="rId657"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J435" r:id="rId658"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I436" r:id="rId659"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I437" r:id="rId660"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I438" r:id="rId661"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I439" r:id="rId662"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I440" r:id="rId663"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I441" r:id="rId664"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J441" r:id="rId665"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I442" r:id="rId666"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J442" r:id="rId667"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J443" r:id="rId668"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J444" r:id="rId669"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J445" r:id="rId670"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I446" r:id="rId671"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J446" r:id="rId672"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I447" r:id="rId673"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J447" r:id="rId674"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I448" r:id="rId675"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J448" r:id="rId676"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J449" r:id="rId677"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J450" r:id="rId678"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I454" r:id="rId679"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J454" r:id="rId680"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I455" r:id="rId681"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J455" r:id="rId682"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I456" r:id="rId683"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J456" r:id="rId684"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I457" r:id="rId685"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J457" r:id="rId686"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I459" r:id="rId687"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J459" r:id="rId688"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I460" r:id="rId689"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J460" r:id="rId690"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I461" r:id="rId691"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J461" r:id="rId692"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I462" r:id="rId693"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J462" r:id="rId694"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I463" r:id="rId695"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J463" r:id="rId696"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I464" r:id="rId697"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J464" r:id="rId698"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I465" r:id="rId699"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J465" r:id="rId700"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I466" r:id="rId701"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J466" r:id="rId702"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I467" r:id="rId703"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J467" r:id="rId704"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I468" r:id="rId705"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I469" r:id="rId706"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J469" r:id="rId707"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I470" r:id="rId708"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J470" r:id="rId709"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I471" r:id="rId710"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J471" r:id="rId711"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I472" r:id="rId712"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J472" r:id="rId713"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I473" r:id="rId714"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J473" r:id="rId715"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I474" r:id="rId716"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J474" r:id="rId717"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I476" r:id="rId718"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J476" r:id="rId719"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I477" r:id="rId720"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I478" r:id="rId721"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J478" r:id="rId722"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I479" r:id="rId723"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J479" r:id="rId724"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I480" r:id="rId725"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J480" r:id="rId726"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I481" r:id="rId727"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J481" r:id="rId728"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J482" r:id="rId729"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I483" r:id="rId730"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J483" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J30" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J43" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J44" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I50" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I52" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I53" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J53" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J54" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J56" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J57" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J58" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J59" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J60" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J61" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J62" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J63" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I64" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J64" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J65" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J66" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J67" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J68" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J69" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J70" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I78" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I79" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I80" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I81" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I83" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I84" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I85" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I86" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I87" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I88" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I89" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I90" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I91" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I92" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J92" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I93" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I94" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J94" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I95" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I96" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I97" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J97" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I98" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J98" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I99" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J99" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I100" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J100" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I101" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J101" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I103" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J103" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I104" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J104" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I105" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J105" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I106" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J106" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I107" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J107" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I108" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J108" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I109" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J109" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I110" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I111" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J111" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I112" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I113" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I114" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I115" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I116" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J116" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I117" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I118" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I119" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I120" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I121" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I122" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I123" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I124" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I125" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I126" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I127" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J127" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I128" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J128" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I129" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J129" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I130" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J130" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I131" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J131" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I132" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J132" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I133" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J133" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I134" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J134" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I135" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J135" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I136" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I137" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J137" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I138" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J138" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I139" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J139" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I140" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J140" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I141" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I142" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I143" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I144" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I145" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I146" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J146" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I147" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J147" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I148" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I149" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I150" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I151" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I152" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I153" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I154" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J154" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I155" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J155" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I156" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J156" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I157" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I158" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I159" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I160" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J160" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I161" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J161" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I162" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J162" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I163" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J163" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I164" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J164" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I165" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J165" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I166" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J166" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I167" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J167" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I168" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J168" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I170" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J170" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I171" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J171" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I172" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J172" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I173" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J173" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I174" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J174" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I175" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J175" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I176" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J176" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J193" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I199" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I200" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I201" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I202" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I203" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I204" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I205" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I206" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I207" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I208" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I209" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I210" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I211" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I212" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I213" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I214" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I215" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I216" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I217" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I218" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I219" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J219" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I220" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J220" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I221" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J221" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I222" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J222" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I223" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J223" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I224" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J224" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I225" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J225" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I226" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J226" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I227" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J227" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I228" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J228" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I229" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J229" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I230" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J230" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I231" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J231" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I232" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J232" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I233" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J233" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I234" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J234" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I235" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J235" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I236" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J236" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I237" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J237" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I238" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I239" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I240" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J240" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I241" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J241" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I242" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J242" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I243" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J243" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I244" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J244" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I245" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J245" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I246" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J246" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I247" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J247" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I248" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J248" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I249" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J249" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I250" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J250" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I251" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J251" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I252" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J252" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I253" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J253" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I254" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J254" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I255" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J255" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I256" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J256" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I257" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J257" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I258" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J258" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I259" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J259" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J260" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I261" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J261" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I262" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J262" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I263" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J263" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I264" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J264" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I265" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I266" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I267" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J267" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I268" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I269" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J269" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I270" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J270" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I271" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J271" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I272" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J272" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I273" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J273" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I274" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I275" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J275" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I276" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J276" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I277" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I278" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I279" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I280" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I281" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I282" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I283" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I284" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J284" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I285" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J285" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I286" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J286" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I287" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J287" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I288" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J288" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I289" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J289" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I290" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J290" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I291" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J291" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I292" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J292" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I293" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J293" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I294" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J294" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I295" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J295" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I296" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J296" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I297" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J297" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I298" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J298" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I299" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J299" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I300" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J300" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I301" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J301" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I302" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J302" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I303" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J303" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I304" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J304" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I305" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J305" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I306" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J306" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I307" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J307" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I308" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J308" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I309" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J309" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I310" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J310" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I311" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J311" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I312" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J312" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I313" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J313" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I314" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J314" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I315" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J315" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I316" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J316" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I317" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J317" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I318" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J318" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I319" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J319" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I320" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J320" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I321" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J321" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I322" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J322" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I323" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J323" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I324" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I325" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I326" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I327" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I328" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I329" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I330" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I331" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J332" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I333" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I334" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I335" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I336" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I337" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I338" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I339" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I340" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J340" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I341" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J341" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I342" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J342" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I343" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J343" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I344" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J344" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I345" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J345" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I346" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J346" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I347" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J347" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I348" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J348" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I349" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I350" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J350" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I351" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J351" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I352" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J352" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I354" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J354" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I355" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J355" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I356" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J356" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I357" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J357" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I358" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J358" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I359" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J359" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I360" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J360" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I361" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I362" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I363" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I364" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I365" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I366" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J366" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I367" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J367" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I368" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J368" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I369" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J369" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I370" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J370" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I371" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J371" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I372" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J372" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I373" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J373" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I374" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J374" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I375" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J375" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I376" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J376" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I377" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J377" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I378" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J378" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I379" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J379" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I380" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J380" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I381" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J381" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I382" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J382" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I383" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J383" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I384" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J384" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I385" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J385" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I386" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J386" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J387" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J388" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I389" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J389" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I390" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J390" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I391" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J391" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I392" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J392" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I393" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I394" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I395" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I396" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I397" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I398" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I399" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I400" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I401" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I402" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I403" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I404" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J404" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I405" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I406" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I407" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I408" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I409" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J409" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I410" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J410" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I411" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J411" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I412" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J412" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I413" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J413" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I415" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J415" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I416" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J416" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I417" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J417" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I418" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J418" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I419" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J419" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I420" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J420" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I421" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J421" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I422" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J422" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I423" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J423" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I424" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J424" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I425" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J425" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I426" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J426" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I427" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J427" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I428" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J428" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I429" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J429" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I430" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J430" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I431" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J431" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I432" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J432" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I434" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J434" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I435" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J435" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I436" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I437" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I438" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I439" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I440" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I441" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J441" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I442" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J442" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J443" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J444" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J445" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I446" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J446" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I447" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J447" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I448" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J448" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J449" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J450" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I454" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J454" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I455" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J455" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I456" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J456" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I457" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J457" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I459" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J459" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I460" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J460" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I461" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J461" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I462" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J462" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I463" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J463" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I464" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J464" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I465" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J465" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I466" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J466" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I467" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J467" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I468" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I469" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J469" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I470" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J470" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I471" r:id="rId725"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J471" r:id="rId726"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I472" r:id="rId727"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J472" r:id="rId728"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I473" r:id="rId729"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J473" r:id="rId730"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I474" r:id="rId731"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J474" r:id="rId732"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I476" r:id="rId733"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J476" r:id="rId734"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I477" r:id="rId735"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I478" r:id="rId736"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J478" r:id="rId737"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I479" r:id="rId738"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J479" r:id="rId739"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I480" r:id="rId740"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J480" r:id="rId741"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I481" r:id="rId742"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J481" r:id="rId743"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J482" r:id="rId744"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I483" r:id="rId745"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J483" r:id="rId746"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25081,7 +25324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25216,13 +25459,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>INTROUVABLE</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>TROUVE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>morningstar</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>28/02/2022</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>https://doc.morningstar.com/LatestDoc.aspx?clientid=unience&amp;key=21a2546a9b5481a0&amp;language=451&amp;investmentid=F00000NMTJ&amp;documenttype=52&amp;investmenttype=1&amp;frame=0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -25232,7 +25494,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Aucun 'MonthlyFactsheet' dans l'API documents Amundi (sites lu/fr/de/es/ch/ie) ; seule une 'SubfundWeeklyFactsheet' du 22/03/2023 (très ancienne, non retenue) : https://www.amundi.lu/dl/doc/subfund-weekly-factsheet/IE00B61N8946/ENG/AMUNDI/20230322. Site metori.com sans reporting public ; Morningstar non joignable (anti-bot).</t>
+          <t>Seule factsheet trouvée : Monthly report Lyxor Epsilon Global Trend - Class A EUR au 28/02/2022 via Morningstar (SecId F00000NMTJ), ISIN présent. TRÈS ANCIENNE (&gt; 4 ans) : plus de reporting publié depuis (fonds possiblement fermé/sans distribution). La 'SubfundWeeklyFactsheet' Amundi du 22/03/2023 est en fait une note SVB/Credit Suisse, pas une fiche. fundinfo : pas de MR.</t>
         </is>
       </c>
     </row>
@@ -25265,7 +25527,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Fonds Apicil Trésorerie GAC géré par Groupama AM (confirmé Morningstar) mais absent de la base produits publique groupama-am.com (API ProductAPI/DocumentAPI : aucun produit pour cet ISIN) ; URLs Reporting_mensuel_des_OPC_French_FR0012534840_2026-09/10-JJ.pdf testées : 404. Site apicil-am.com injoignable. Probablement fonds dédié (Apicil) sans reporting public.</t>
+          <t>Fonds Apicil Trésorerie GAC géré par Groupama AM (confirmé Morningstar) mais absent de la base produits publique groupama-am.com (API ProductAPI/DocumentAPI : aucun produit pour cet ISIN) ; URLs Reporting_mensuel_des_OPC_French_FR0012534840_2026-09/10-JJ.pdf testées : 404. Site apicil-am.com injoignable. Probablement fonds dédié (Apicil) sans reporting public. | Passe fix : fundinfo (FR/LU/DE/CH/BE-priv) sans fiche mensuelle (MR) ; Morningstar LatestDoc type 52 : 404.</t>
         </is>
       </c>
     </row>
@@ -25336,7 +25598,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Page fonds AXA IM existe (ISIN LU2485150747 dans la page) mais documents chargés en JS (Kurtosys), non accessibles par curl; Morningstar (SecId F00001DZ9K) sans factsheet (404). Part institutionnelle BX. Gestion désormais BNP Paribas AM.</t>
+          <t>Page fonds AXA IM existe (ISIN LU2485150747 dans la page) mais documents chargés en JS (Kurtosys), non accessibles par curl; Morningstar (SecId F00001DZ9K) sans factsheet (404). Part institutionnelle BX. Gestion désormais BNP Paribas AM. | Passe fix : fundinfo (FR/LU/DE/CH/BE-priv) sans fiche mensuelle (MR) ; Morningstar LatestDoc type 52 : 404.</t>
         </is>
       </c>
     </row>
@@ -25442,7 +25704,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>La page de la part LU1502282632 renvoie 403 (profils LU/FR/BE/IT/DE/ES/CH) : part peut-être fermée/non distribuée. Seul le rapport mensuel du compartiment au 30/09/2026 a été trouvé, mais il couvre la classe C (USD) LU1502282558 et D LU1502282715 — ISIN demandé absent.</t>
+          <t>La page de la part LU1502282632 renvoie 403 (profils LU/FR/BE/IT/DE/ES/CH) : part peut-être fermée/non distribuée. Seul le rapport mensuel du compartiment au 30/09/2026 a été trouvé, mais il couvre la classe C (USD) LU1502282558 et D LU1502282715 — ISIN demandé absent. | Passe fix : fundinfo (FR/LU/DE/CH/BE-priv) sans fiche mensuelle (MR) ; Morningstar LatestDoc type 52 : 404. fundinfo n'a qu'un commentaire mensuel du compartiment (MC, août 2026) sans la part.</t>
         </is>
       </c>
     </row>
@@ -25682,22 +25944,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LU1244893696</t>
+          <t>XFCS00OL1456</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EDMOND DE ROTHSCHILD FUND BIG DATA A EUR</t>
+          <t>FAF GLOBAL BALANCED PORTFOLIO EUR C</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>EDMOND DE ROTHSCHILD ASSET MANAGEMENT LUXEMBOURG</t>
+          <t xml:space="preserve">Fiducenter S.A. </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>INTROUVABLE</t>
+          <t>FONDS_INTERNE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -25708,29 +25970,29 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Site EdR AM (am.edmond-de-rothschild.com, funds.edram.com redirige) protégé par Cloudflare (403 challenge JS) et non résolu par WebFetch ; pas d'URL de factsheet directe trouvée ; agrégateur ebnbanco.com : seulement DIC/prospectus/rapports, pas de factsheet.</t>
+          <t>Code XFCS = fonds interne d'assurance-vie (pas un ISIN public) ; rien sur fiducenter.lu (pages et médias WordPress) ni Morningstar (screener vide).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LU1161526576</t>
+          <t>XFCS000OL258</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EDRF BOND ALLOCATION R EUR</t>
+          <t>FIC ALL WEATHER GLOBAL BALANCED ALLOCATION A</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>EDMOND DE ROTHSCHILD ASSET MANAGEMENT LUXEMBOURG</t>
+          <t>First Trust Global Portfolios Limited</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>INTROUVABLE</t>
+          <t>FONDS_INTERNE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -25741,29 +26003,29 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Site EdR AM (am.edmond-de-rothschild.com, funds.edram.com redirige) protégé par Cloudflare (403 challenge JS) et non résolu par WebFetch ; pas d'URL de factsheet directe trouvée ; agrégateur ebnbanco.com : seulement DIC/prospectus/rapports, pas de factsheet.</t>
+          <t>Code XFCS = fonds interne d'assurance (pas un ISIN public); aucune factsheet publique côté gestionnaire. Non recherché plus avant conformément à la consigne.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LU1160356009</t>
+          <t>XFCS00OL1790</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EDRF HEALTHCARE A EUR</t>
+          <t>FIC DELCAP DIVERSIFIED BOND OPPORTUNITIES</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EDMOND DE ROTHSCHILD ASSET MANAGEMENT LUXEMBOURG</t>
+          <t>DELCAP S.A.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>INTROUVABLE</t>
+          <t>FONDS_INTERNE</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -25774,24 +26036,24 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Site EdR AM (am.edmond-de-rothschild.com, funds.edram.com redirige) protégé par Cloudflare (403 challenge JS) et non résolu par WebFetch ; pas d'URL de factsheet directe trouvée ; agrégateur ebnbanco.com : seulement DIC/prospectus/rapports, pas de factsheet.</t>
+          <t>Fonds interne d'assurance (ISIN XFCS…) : aucune factsheet publique ; site delcap inaccessible (proxy 502).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>XFCS00OL1456</t>
+          <t>XFCS00OL1641</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FAF GLOBAL BALANCED PORTFOLIO EUR C</t>
+          <t>FIC DELCAP LIFESTYLE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fiducenter S.A. </t>
+          <t>DELCAP S.A.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -25807,24 +26069,24 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Code XFCS = fonds interne d'assurance-vie (pas un ISIN public) ; rien sur fiducenter.lu (pages et médias WordPress) ni Morningstar (screener vide).</t>
+          <t>Fonds interne d'assurance (ISIN XFCS…) : aucune factsheet publique ; site delcap inaccessible (proxy 502).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>XFCS000OL258</t>
+          <t>XFCS00OL1561</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FIC ALL WEATHER GLOBAL BALANCED ALLOCATION A</t>
+          <t>FIC DNCA INFLATION TREND</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>First Trust Global Portfolios Limited</t>
+          <t>DNCA FINANCE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -25840,24 +26102,24 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Code XFCS = fonds interne d'assurance (pas un ISIN public); aucune factsheet publique côté gestionnaire. Non recherché plus avant conformément à la consigne.</t>
+          <t>Code XFCS = fonds interne d'assurance (FIC), pas de factsheet publique chez DNCA.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>XFCS00OL1790</t>
+          <t>XFCS000OL284</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FIC DELCAP DIVERSIFIED BOND OPPORTUNITIES</t>
+          <t>FIC ESSENTIA EQUILIBRE B</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DELCAP S.A.</t>
+          <t>Banque de Luxembourg Investissement (BLI)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -25873,24 +26135,24 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Fonds interne d'assurance (ISIN XFCS…) : aucune factsheet publique ; site delcap inaccessible (proxy 502).</t>
+          <t>Code XFCS = fonds interne collectif d'assurance (pas un vrai ISIN) ; aucune mention 'Essentia' sur le site BLI (banquedeluxembourginvestments.com) ; reporting éventuellement disponible seulement auprès de l'assureur.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>XFCS00OL1641</t>
+          <t>XFCS000OL283</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FIC DELCAP LIFESTYLE</t>
+          <t>FIC ESSENTIA PRUDENT B</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DELCAP S.A.</t>
+          <t>Banque de Luxembourg Investissement (BLI)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -25906,24 +26168,24 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Fonds interne d'assurance (ISIN XFCS…) : aucune factsheet publique ; site delcap inaccessible (proxy 502).</t>
+          <t>Code XFCS = fonds interne collectif d'assurance (pas un vrai ISIN) ; aucune mention 'Essentia' sur le site BLI (banquedeluxembourginvestments.com) ; reporting éventuellement disponible seulement auprès de l'assureur.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>XFCS00OL1561</t>
+          <t>XFCS00OL2045</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FIC DNCA INFLATION TREND</t>
+          <t>FIC FAIRWIN EVOLUTION</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DNCA FINANCE</t>
+          <t>Rothschild &amp; Co Asset Management Europe</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -25939,24 +26201,24 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Code XFCS = fonds interne d'assurance (FIC), pas de factsheet publique chez DNCA.</t>
+          <t>Code XFCS = fonds interne collectif d'assurance-vie, pas un ISIN public ; absent de l'API fonds Rothschild AM, aucune factsheet publique.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>XFCS000OL284</t>
+          <t>XFCS00OL2157</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FIC ESSENTIA EQUILIBRE B</t>
+          <t>FIC GOLDMAN SACHS ALPHA ENHANCED ETF CAM</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Banque de Luxembourg Investissement (BLI)</t>
+          <t>Invest4Growth Asset Management Ltd</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -25972,24 +26234,24 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Code XFCS = fonds interne collectif d'assurance (pas un vrai ISIN) ; aucune mention 'Essentia' sur le site BLI (banquedeluxembourginvestments.com) ; reporting éventuellement disponible seulement auprès de l'assureur.</t>
+          <t>Invest4Growth (i4gam.com) : fonds interne d'assurance (code XFCS), aucune factsheet publiée sur le site (pages Documents / Investment Results / Fonds dédiés vérifiées) ni sur fundinfo.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>XFCS000OL283</t>
+          <t>XFCS000OL243</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FIC ESSENTIA PRUDENT B</t>
+          <t>FIC HERMITAGE PATRIMOINE B</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Banque de Luxembourg Investissement (BLI)</t>
+          <t>PRIVALUX MANAGEMENT S.A.</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -26005,24 +26267,24 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Code XFCS = fonds interne collectif d'assurance (pas un vrai ISIN) ; aucune mention 'Essentia' sur le site BLI (banquedeluxembourginvestments.com) ; reporting éventuellement disponible seulement auprès de l'assureur.</t>
+          <t>Code XFCS = fonds interne collectif d'assurance (FIC), sans ISIN public ; aucune factsheet publique trouvée (site Privalux privalux.com inaccessible : certificat TLS invalide).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>XFCS00OL2045</t>
+          <t>XFCS000OL309</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FIC FAIRWIN EVOLUTION</t>
+          <t>FIC HORIZON B</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rothschild &amp; Co Asset Management Europe</t>
+          <t>Andbank Luxembourg</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -26038,24 +26300,24 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Code XFCS = fonds interne collectif d'assurance-vie, pas un ISIN public ; absent de l'API fonds Rothschild AM, aucune factsheet publique.</t>
+          <t>Code XFCS = fonds interne collectif (FIC) d'assurance-vie luxembourgeoise, sans factsheet publique ; recherche web sans résultat. Reporting à demander à l'assureur ou à Andbank Luxembourg.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>XFCS00OL2157</t>
+          <t>XFCS000OL271</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FIC GOLDMAN SACHS ALPHA ENHANCED ETF CAM</t>
+          <t>FIC L HARMONY BOREAL FUND</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Invest4Growth Asset Management Ltd</t>
+          <t>PRIVALUX MANAGEMENT S.A.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -26071,24 +26333,24 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Invest4Growth (i4gam.com) : fonds interne d'assurance (code XFCS), aucune factsheet publiée sur le site (pages Documents / Investment Results / Fonds dédiés vérifiées) ni sur fundinfo.</t>
+          <t>Code XFCS = fonds interne collectif d'assurance (FIC), sans ISIN public ; aucune factsheet publique trouvée (site Privalux privalux.com inaccessible : certificat TLS invalide).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>XFCS000OL243</t>
+          <t>XFCS00OL1425</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FIC HERMITAGE PATRIMOINE B</t>
+          <t>FIC MONETARY PLUS STRATEGY FUND</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PRIVALUX MANAGEMENT S.A.</t>
+          <t>Invest4Growth Asset Management Ltd</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -26104,24 +26366,24 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Code XFCS = fonds interne collectif d'assurance (FIC), sans ISIN public ; aucune factsheet publique trouvée (site Privalux privalux.com inaccessible : certificat TLS invalide).</t>
+          <t>Invest4Growth (i4gam.com) : fonds interne d'assurance (code XFCS), aucune factsheet publiée sur le site (pages Documents / Investment Results / Fonds dédiés vérifiées) ni sur fundinfo.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>XFCS000OL309</t>
+          <t>XFCS000OL228</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FIC HORIZON B</t>
+          <t>FIC MS REAL ESTATE FUND A</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Andbank Luxembourg</t>
+          <t>Montségur</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -26137,24 +26399,24 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Code XFCS = fonds interne collectif (FIC) d'assurance-vie luxembourgeoise, sans factsheet publique ; recherche web sans résultat. Reporting à demander à l'assureur ou à Andbank Luxembourg.</t>
+          <t>Code XFCS = fonds interne collectif d'assurance (FIC), sans ISIN public ; aucune factsheet publique trouvée chez Montségur.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>XFCS000OL271</t>
+          <t>XFCS00OL1887</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FIC L HARMONY BOREAL FUND</t>
+          <t>FIC PATRIMOINE LIFE DYNAMIC FUND A</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PRIVALUX MANAGEMENT S.A.</t>
+          <t xml:space="preserve">Fiducenter S.A. </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -26170,24 +26432,24 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Code XFCS = fonds interne collectif d'assurance (FIC), sans ISIN public ; aucune factsheet publique trouvée (site Privalux privalux.com inaccessible : certificat TLS invalide).</t>
+          <t>Code XFCS = fonds interne collectif d'assurance-vie ; aucune factsheet publique sur fiducenter.lu ni Morningstar.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>XFCS00OL1425</t>
+          <t>XFCS00OL1797</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FIC MONETARY PLUS STRATEGY FUND</t>
+          <t>FIC PATRIMOINE LIFE PRUDENCE FUND</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Invest4Growth Asset Management Ltd</t>
+          <t xml:space="preserve">Fiducenter S.A. </t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -26203,24 +26465,24 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Invest4Growth (i4gam.com) : fonds interne d'assurance (code XFCS), aucune factsheet publiée sur le site (pages Documents / Investment Results / Fonds dédiés vérifiées) ni sur fundinfo.</t>
+          <t>Code XFCS = fonds interne collectif d'assurance-vie ; aucune factsheet publique sur fiducenter.lu ni Morningstar.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>XFCS000OL228</t>
+          <t>XFCS000OL264</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FIC MS REAL ESTATE FUND A</t>
+          <t>FIC PATRIMONIAL ADVICE FUND</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Montségur</t>
+          <t>Andbank Luxembourg</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -26236,24 +26498,24 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Code XFCS = fonds interne collectif d'assurance (FIC), sans ISIN public ; aucune factsheet publique trouvée chez Montségur.</t>
+          <t>Code XFCS = fonds interne collectif (FIC) d'assurance-vie luxembourgeoise, sans factsheet publique ; recherche web sans résultat. Reporting à demander à l'assureur ou à Andbank Luxembourg.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>XFCS00OL1887</t>
+          <t>XFCS00OL1454</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FIC PATRIMOINE LIFE DYNAMIC FUND A</t>
+          <t>FIC PURE EQUILIBRE 2.0</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fiducenter S.A. </t>
+          <t>Pure Capital S.A.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -26267,26 +26529,31 @@
           <t>non</t>
         </is>
       </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>https://www.purecapital.eu/wealth-management/nos-solutions-en-detail/solution-multifonds-2-0/profil-equilibre.html</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Code XFCS = fonds interne collectif d'assurance-vie ; aucune factsheet publique sur fiducenter.lu ni Morningstar.</t>
+          <t>ISIN XFCS = fonds interne d'assurance (FIC). Page Pure Capital 'Solution Multifonds 2.0 – Profil Équilibré' sans factsheet téléchargeable.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>XFCS00OL1797</t>
+          <t>XFCS000OL244</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FIC PATRIMOINE LIFE PRUDENCE FUND</t>
+          <t>FIC SOLID CAPTAIN</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fiducenter S.A. </t>
+          <t>GAM Investments</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -26302,24 +26569,24 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Code XFCS = fonds interne collectif d'assurance-vie ; aucune factsheet publique sur fiducenter.lu ni Morningstar.</t>
+          <t>Code XFCS = fonds interne collectif d'assurance-vie (géré par GAM) ; absent de Morningstar, aucune factsheet publique.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>XFCS000OL264</t>
+          <t>XFCS00OL2130</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FIC PATRIMONIAL ADVICE FUND</t>
+          <t>FIC SOLID COMPASS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Andbank Luxembourg</t>
+          <t>CARMIGNAC_AM_FIC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -26335,24 +26602,24 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Code XFCS = fonds interne collectif (FIC) d'assurance-vie luxembourgeoise, sans factsheet publique ; recherche web sans résultat. Reporting à demander à l'assureur ou à Andbank Luxembourg.</t>
+          <t>Code XFCS = fonds interne collectif d'assurance (FIC), sans ISIN public ; aucune factsheet publique trouvée (FIC géré par Carmignac ; code au format atypique XFCS00OL2130).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>XFCS00OL1454</t>
+          <t>XFCS000OL288</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FIC PURE EQUILIBRE 2.0</t>
+          <t>FIC SOLID SEA FUND</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pure Capital S.A.</t>
+          <t>Lazard Frères Gestion</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -26366,31 +26633,26 @@
           <t>non</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>https://www.purecapital.eu/wealth-management/nos-solutions-en-detail/solution-multifonds-2-0/profil-equilibre.html</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>ISIN XFCS = fonds interne d'assurance (FIC). Page Pure Capital 'Solution Multifonds 2.0 – Profil Équilibré' sans factsheet téléchargeable.</t>
+          <t>Code XFCS = fonds interne d'assurance (FIC), pas de factsheet publique chez Lazard Frères Gestion.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>XFCS000OL244</t>
+          <t>XFCS000OL247</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FIC SOLID CAPTAIN</t>
+          <t>FIC SOMAFI NEUTRAL B</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GAM Investments</t>
+          <t>PRIVALUX MANAGEMENT S.A.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -26406,24 +26668,24 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Code XFCS = fonds interne collectif d'assurance-vie (géré par GAM) ; absent de Morningstar, aucune factsheet publique.</t>
+          <t>Code XFCS = fonds interne collectif d'assurance (FIC), sans ISIN public ; aucune factsheet publique trouvée (site Privalux privalux.com inaccessible : certificat TLS invalide).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>XFCS00OL2130</t>
+          <t>XFCS00OL1729</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FIC SOLID COMPASS</t>
+          <t>FIC VIVACITY FLEXIBLE PORTFOLIO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CARMIGNAC_AM_FIC</t>
+          <t>INTESA SANPAOLO WEALTH MANAGEMENT</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -26439,62 +26701,86 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Code XFCS = fonds interne collectif d'assurance (FIC), sans ISIN public ; aucune factsheet publique trouvée (FIC géré par Carmignac ; code au format atypique XFCS00OL2130).</t>
+          <t>ISIN XFCS = fonds interne d'assurance (FIC) Intesa Sanpaolo Wealth Management; aucune factsheet publique repérée (recherche rapide).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>XFCS000OL288</t>
+          <t>LU0854762894</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FIC SOLID SEA FUND</t>
+          <t>IFP GLOBAL AGE EUR</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lazard Frères Gestion</t>
+          <t>IFP Investment Management S.A.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FONDS_INTERNE</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
+          <t>TROUVE</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>morningstar</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>31/07/2020</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://doc.morningstar.com/LatestDoc.aspx?clientid=unience&amp;key=21a2546a9b5481a0&amp;language=451&amp;investmentid=F00000S5AK&amp;documenttype=52&amp;investmenttype=1&amp;frame=0</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>https://www.ifpim.lu/services-eng</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Code XFCS = fonds interne d'assurance (FIC), pas de factsheet publique chez Lazard Frères Gestion.</t>
+          <t>Seule factsheet trouvée: 'IFP Global Age Fund Class EUR - July 31, 2020' via Morningstar, ISIN présent. TRÈS ANCIENNE (&gt;6 ans) ; site IFPIM ne publie aucune factsheet.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>XFCS000OL247</t>
+          <t>FR001400SJA2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FIC SOMAFI NEUTRAL B</t>
+          <t>IVO IG 2030 R EUR</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PRIVALUX MANAGEMENT S.A.</t>
+          <t>IVO Capital Partners</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FONDS_INTERNE</t>
+          <t>INTROUVABLE</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -26503,59 +26789,88 @@
           <t>non</t>
         </is>
       </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>https://www.ivocapital.com/fonds/ivo-ig-2030/?isin=FR001400SJA2</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Code XFCS = fonds interne collectif d'assurance (FIC), sans ISIN public ; aucune factsheet publique trouvée (site Privalux privalux.com inaccessible : certificat TLS invalide).</t>
+          <t>Page fonds trouvée sur ivocapital.com, mais la liste des reportings est chargée via admin-ajax protégé par un challenge JavaScript anti-robot (o2switch Tiger Protect) ; aucune URL de PDF visible ; recherche web sans reporting. À récupérer manuellement depuis un navigateur.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>XFCS00OL1729</t>
+          <t>FR0007028543</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FIC VIVACITY FLEXIBLE PORTFOLIO</t>
+          <t>LAZARD PATRIMOINE OPPORTUNITIES SRI RC EUR</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>INTESA SANPAOLO WEALTH MANAGEMENT</t>
+          <t>Lazard Frères Gestion</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FONDS_INTERNE</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>TROUVE</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>gestionnaire</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>31/10/2025</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://www.lazardassetmanagement.com/docs/191148/FR0007028543_Factsheet_French%20(France).pdf</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>https://www.lazardfreresgestion.com/fr/fr_fr/fonds/fond-details/16/3807.html</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>ISIN XFCS = fonds interne d'assurance (FIC) Intesa Sanpaolo Wealth Management; aucune factsheet publique repérée (recherche rapide).</t>
+          <t>ANCIENNE (10-2025, mois seul) : seule factsheet trouvée pour la part RC ; la page fonds actuelle ne liste plus de reporting mensuel pour ce fonds.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LU0854762894</t>
+          <t>FR0012355139</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>IFP GLOBAL AGE EUR</t>
+          <t>LAZARD PATRIMOINE SRI RC EUR</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>IFP Investment Management S.A.</t>
+          <t>Lazard Frères Gestion</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -26565,12 +26880,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>morningstar</t>
+          <t>gestionnaire</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>31/07/2020</t>
+          <t>31/10/2025</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -26585,39 +26900,49 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://doc.morningstar.com/LatestDoc.aspx?clientid=unience&amp;key=21a2546a9b5481a0&amp;language=451&amp;investmentid=F00000S5AK&amp;documenttype=52&amp;investmenttype=1&amp;frame=0</t>
+          <t>https://www.lazardassetmanagement.com/docs/191094/FR0012355139_Factsheet_English%20(UK).pdf</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://www.ifpim.lu/services-eng</t>
+          <t>https://www.lazardfreresgestion.com/fr/fr_fr/fonds/fond-details/16/2541.html</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Seule factsheet trouvée: 'IFP Global Age Fund Class EUR - July 31, 2020' via Morningstar, ISIN présent. TRÈS ANCIENNE (&gt;6 ans) ; site IFPIM ne publie aucune factsheet.</t>
+          <t>ANCIENNE (10-2025, mois seul, version EN) : la page fonds liste des reportings 08-2026 pour d'autres parts (ex. PC H USD) mais pas pour la part RC ; aucune version plus récente trouvée.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FR001400SJA2</t>
+          <t>BE6370437590</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IVO IG 2030 R EUR</t>
+          <t>LELEUX INVEST DYNAMIC WORLD FOF PA EUR</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IVO Capital Partners</t>
+          <t>LELEUX FUND MANAGEMENT &amp; PARTNERS S.A.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>INTROUVABLE</t>
+          <t>NON_VERIFIE</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>gestionnaire</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -26626,36 +26951,41 @@
           <t>non</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://www.leleuxinvest.be/Leleux/LeleuxInvest.nsf/0/26E46FDCB6FABEB2C1258E8B003F5314/$File/MR-FR-R-DW-09-2026%20-%20FSMA%20Approved.pdf</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://www.ivocapital.com/fonds/ivo-ig-2030/?isin=FR001400SJA2</t>
+          <t>https://www.leleuxinvest.be/Leleux/LeleuxInvest.nsf/vLUPage/WORLDDYNAMIC?OpenDocument</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Page fonds trouvée sur ivocapital.com, mais la liste des reportings est chargée via admin-ajax protégé par un challenge JavaScript anti-robot (o2switch Tiger Protect) ; aucune URL de PDF visible ; recherche web sans reporting. À récupérer manuellement depuis un navigateur.</t>
+          <t>Leleux Invest ne publie de rapport mensuel que pour la classe R (page MONTHLY-REPORT : RCAP/RDIS uniquement). PDF téléchargé = rapport mensuel Dynamic World FOF classe R Capitalisation (BE6370436584) au 30/09/2026 ; l'ISIN BE6370437590 (classe PA) n'y figure pas. Aucune fiche propre à la classe PA trouvée.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FR0007028543</t>
+          <t>BE6327306930</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LAZARD PATRIMOINE OPPORTUNITIES SRI RC EUR</t>
+          <t>LELEUX INVEST PATRIMONIAL WORLD PA EUR</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lazard Frères Gestion</t>
+          <t>LELEUX FUND MANAGEMENT &amp; PARTNERS S.A.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>TROUVE</t>
+          <t>NON_VERIFIE</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -26665,54 +26995,50 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>31/10/2025</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://www.lazardassetmanagement.com/docs/191148/FR0007028543_Factsheet_French%20(France).pdf</t>
+          <t>https://www.leleuxinvest.be/Leleux/LeleuxInvest.nsf/0/54C370ADC0BCB1F6C1258E8B003F7625/$File/MR-FR-R-PW-09-2026%20-%20FSMA%20Approved.pdf</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.lazardfreresgestion.com/fr/fr_fr/fonds/fond-details/16/3807.html</t>
+          <t>https://www.leleuxinvest.be/Leleux/LeleuxInvest.nsf/vLUPage/WORLDPATRIM?OpenDocument</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>ANCIENNE (10-2025, mois seul) : seule factsheet trouvée pour la part RC ; la page fonds actuelle ne liste plus de reporting mensuel pour ce fonds.</t>
+          <t>Leleux Invest ne publie de rapport mensuel que pour la classe R (page MONTHLY-REPORT : RCAP/RDIS uniquement). PDF téléchargé = rapport mensuel Patrimonial World FOF classe R Capitalisation (BE6286029416) au 30/09/2026 ; l'ISIN BE6327306930 (classe PA) n'y figure pas. Aucune fiche propre à la classe PA trouvée.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FR0012355139</t>
+          <t>BE6327307946</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LAZARD PATRIMOINE SRI RC EUR</t>
+          <t>LELEUX INVEST RESPONSIBLE WORLD PA EUR</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lazard Frères Gestion</t>
+          <t>LELEUX FUND MANAGEMENT &amp; PARTNERS S.A.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>TROUVE</t>
+          <t>NON_VERIFIE</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -26722,49 +27048,45 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>31/10/2025</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://www.lazardassetmanagement.com/docs/191094/FR0012355139_Factsheet_English%20(UK).pdf</t>
+          <t>https://www.leleuxinvest.be/Leleux/LeleuxInvest.nsf/0/34DBE7DEAE290BBCC1258E6E004FAAFE/$File/MR-FR-R-RW-09-2026%20-%20FSMA%20Approved.pdf</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://www.lazardfreresgestion.com/fr/fr_fr/fonds/fond-details/16/2541.html</t>
+          <t>https://www.leleuxinvest.be/Leleux/LeleuxInvest.nsf/vLUPage/WORLDRESPONSIBLE?OpenDocument</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>ANCIENNE (10-2025, mois seul, version EN) : la page fonds liste des reportings 08-2026 pour d'autres parts (ex. PC H USD) mais pas pour la part RC ; aucune version plus récente trouvée.</t>
+          <t>Leleux Invest ne publie de rapport mensuel que pour la classe R (page MONTHLY-REPORT : RCAP/RDIS uniquement). PDF téléchargé = rapport mensuel Responsible World FOF classe R Capitalisation (BE6304593781) au 30/09/2026 ; l'ISIN BE6327307946 (classe PA) n'y figure pas. Aucune fiche propre à la classe PA trouvée.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BE6370437590</t>
+          <t>LU3149167358</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LELEUX INVEST DYNAMIC WORLD FOF PA EUR</t>
+          <t>M&amp;G (LUX) EPISODE MACRO FUND S EUR</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>LELEUX FUND MANAGEMENT &amp; PARTNERS S.A.</t>
+          <t>M&amp;G Luxembourg S.A.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -26775,11 +27097,6 @@
       <c r="E44" t="inlineStr">
         <is>
           <t>gestionnaire</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -26790,49 +27107,34 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://www.leleuxinvest.be/Leleux/LeleuxInvest.nsf/0/26E46FDCB6FABEB2C1258E8B003F5314/$File/MR-FR-R-DW-09-2026%20-%20FSMA%20Approved.pdf</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>https://www.leleuxinvest.be/Leleux/LeleuxInvest.nsf/vLUPage/WORLDDYNAMIC?OpenDocument</t>
+          <t>https://api.fundinfo.com/document/9c2bbf1ed0f324b35d74a95c03fc985c_96104/MR_LU_en_LU3149167358_YES_2026-08-31.pdf?apiKey=b9934aa2-1a83-4286-b11b-c8415da9e581</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Leleux Invest ne publie de rapport mensuel que pour la classe R (page MONTHLY-REPORT : RCAP/RDIS uniquement). PDF téléchargé = rapport mensuel Dynamic World FOF classe R Capitalisation (BE6370436584) au 30/09/2026 ; l'ISIN BE6370437590 (classe PA) n'y figure pas. Aucune fiche propre à la classe PA trouvée.</t>
+          <t>fundinfo (LU-priv) et Morningstar (SecId F00001SEXW) indexent sous cet ISIN la factsheet M&amp;G (Lux) Episode Macro Fund « EUR Class S-H – Accumulation » au 31/08/2026, mais le PDF porte l'ISIN LU1670714226 (S-H, couverte) ; LU3149167358 absent du tableau des parts. Part demandée (S EUR) non identifiée dans le document.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BE6327306930</t>
+          <t>LU3332968026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LELEUX INVEST PATRIMONIAL WORLD PA EUR</t>
+          <t>M&amp;G (LUX) GLOBAL STRATEGIC VALUE A EUR</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LELEUX FUND MANAGEMENT &amp; PARTNERS S.A.</t>
+          <t>M&amp;G Luxembourg S.A.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NON_VERIFIE</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>gestionnaire</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>30/09/2026</t>
+          <t>INTROUVABLE</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -26841,188 +27143,254 @@
           <t>non</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>https://www.leleuxinvest.be/Leleux/LeleuxInvest.nsf/0/54C370ADC0BCB1F6C1258E8B003F7625/$File/MR-FR-R-PW-09-2026%20-%20FSMA%20Approved.pdf</t>
-        </is>
-      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>https://www.leleuxinvest.be/Leleux/LeleuxInvest.nsf/vLUPage/WORLDPATRIM?OpenDocument</t>
+          <t>https://www.mandg.com/investments/professional-investor/en-lu/funds/mg-lux-global-strategic-value-fund/lu3332968026</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Leleux Invest ne publie de rapport mensuel que pour la classe R (page MONTHLY-REPORT : RCAP/RDIS uniquement). PDF téléchargé = rapport mensuel Patrimonial World FOF classe R Capitalisation (BE6286029416) au 30/09/2026 ; l'ISIN BE6327306930 (classe PA) n'y figure pas. Aucune fiche propre à la classe PA trouvée.</t>
+          <t>Page fonds M&amp;G existe (contenu chargé en JS via Kurtosys) mais aucune factsheet trouvée (URL déduites LU/DE/FR/etc. en 404) ; part récente. | Passe fix : fundinfo (FR/LU/DE/CH/BE-priv) sans fiche mensuelle (MR) ; Morningstar LatestDoc type 52 : 404. (SecId F0000288V3)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BE6327307946</t>
+          <t>LU0864714000</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LELEUX INVEST RESPONSIBLE WORLD PA EUR</t>
+          <t>MAINFIRST ABSOLUTE RETURN MULTI ASSET A EUR</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LELEUX FUND MANAGEMENT &amp; PARTNERS S.A.</t>
+          <t>Mainfirst Affiliated Fund Managers S.A.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NON_VERIFIE</t>
+          <t>AUTRE_SOURCE</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>gestionnaire</t>
+          <t>autre</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>30/09/2026</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://www.leleuxinvest.be/Leleux/LeleuxInvest.nsf/0/34DBE7DEAE290BBCC1258E6E004FAAFE/$File/MR-FR-R-RW-09-2026%20-%20FSMA%20Approved.pdf</t>
+          <t>https://assets.finanzfluss.de/hippoverse/documents/LU0864714000-factsheet.pdf</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://www.leleuxinvest.be/Leleux/LeleuxInvest.nsf/vLUPage/WORLDRESPONSIBLE?OpenDocument</t>
+          <t>https://www.ethenea.com/de-de/mainfirst-absolute-return-multi-asset/</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Leleux Invest ne publie de rapport mensuel que pour la classe R (page MONTHLY-REPORT : RCAP/RDIS uniquement). PDF téléchargé = rapport mensuel Responsible World FOF classe R Capitalisation (BE6304593781) au 30/09/2026 ; l'ISIN BE6327307946 (classe PA) n'y figure pas. Aucune fiche propre à la classe PA trouvée.</t>
+          <t>Factsheet ETHENEA (DE, part A, ISIN présent) au 27/02/2026 hébergée par finanzfluss : ANCIENNE (&gt;3 mois). Compartiment absorbé par LAIQON SICAV le 01/10/2026 (avis ETHENEA du 02/10/2026) ; plus de factsheet sur le site ETHENEA (404).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LU3149167358</t>
+          <t>LU0864709349</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>M&amp;G (LUX) EPISODE MACRO FUND S EUR</t>
+          <t>MAINFIRST GLOBAL EQUITIES FUND A EUR</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>M&amp;G Luxembourg S.A.</t>
+          <t>Mainfirst Affiliated Fund Managers S.A.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>INTROUVABLE</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>AUTRE_SOURCE</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://assets.finanzfluss.de/hippoverse/documents/LU0864709349-factsheet.pdf</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>https://www.ethenea.com/de-de/mainfirst-global-equities-fund/</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Aucune factsheet M&amp;G pour LU3149167358 (URL déduites en 404, recherche web sans résultat). La factsheet de la part USD S (LU1670713921, au 31/08/2026) ne liste pas cette part.</t>
+          <t>Factsheet ETHENEA (DE, part A, ISIN présent) au 27/02/2026 hébergée par finanzfluss : ANCIENNE (&gt;3 mois). Compartiment absorbé par LAIQON SICAV le 01/10/2026 (avis ETHENEA du 02/10/2026) ; plus de factsheet sur le site ETHENEA (404).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>LU1670713335</t>
+          <t>LU1856130205</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>M&amp;G (LUX) GLOBAL CORPORATE BOND FUND A-H EUR</t>
+          <t>MAINFIRST GLOBAL EQUITIES UNCONSTRAINED A EUR</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>M&amp;G Luxembourg S.A.</t>
+          <t>Mainfirst Affiliated Fund Managers S.A.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>INTROUVABLE</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>AUTRE_SOURCE</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>autre</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://assets.finanzfluss.de/hippoverse/documents/LU1856130205-factsheet.pdf</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>https://www.ethenea.com/de-de/mainfirst-global-equities-unconstrained-fund/</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Aucune factsheet M&amp;G (URL déduites en 404 dans 17 pays) ; fonds possiblement fermé/fusionné (seule trace : UK Reporting 2019).</t>
+          <t>Factsheet ETHENEA (DE, part A, ISIN présent) au 27/02/2026 hébergée par finanzfluss : ANCIENNE (&gt;3 mois). Compartiment absorbé par LAIQON SICAV le 01/10/2026 (avis ETHENEA du 02/10/2026) ; plus de factsheet sur le site ETHENEA (404).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>LU3332968026</t>
+          <t>LU2381585830</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>M&amp;G (LUX) GLOBAL STRATEGIC VALUE A EUR</t>
+          <t>MAINFIRST MEGATRENDS ASIA A USD</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>M&amp;G Luxembourg S.A.</t>
+          <t>ETHENEA Independent Investors S.A.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>INTROUVABLE</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
+          <t>TROUVE</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>morningstar</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://doc.morningstar.com/LatestDoc.aspx?clientid=unience&amp;key=21a2546a9b5481a0&amp;language=451&amp;investmentid=F00001CXFD&amp;documenttype=52&amp;investmenttype=1&amp;frame=0</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://www.mandg.com/investments/professional-investor/en-lu/funds/mg-lux-global-strategic-value-fund/lu3332968026</t>
+          <t>https://www.ethenea.com/en-lu/_mainfirst-funds/mainfirst-megatrends-asia/</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Page fonds M&amp;G existe (contenu chargé en JS via Kurtosys) mais aucune factsheet trouvée (URL déduites LU/DE/FR/etc. en 404) ; part récente.</t>
+          <t>Factsheet MainFirst - Megatrends Asia (A) via Morningstar (SecId F00001CXFD), « Factsheet as of 27 February 2026 », ISIN présent. ANCIENNE (&gt; 3 mois) ; fonds absorbé par LAIQON SICAV - Megatrends Asia au 01/10/2026 (avis ETHENEA 02/10/2026). fundinfo : pas de MR.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>LU0864714000</t>
+          <t>LU0308864023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>MAINFIRST ABSOLUTE RETURN MULTI ASSET A EUR</t>
+          <t>MAINFIRST TOP EUROPEAN IDEAS A EUR</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -27032,17 +27400,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>AUTRE_SOURCE</t>
+          <t>TROUVE</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>autre</t>
+          <t>gestionnaire</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -27057,106 +27425,82 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>https://assets.finanzfluss.de/hippoverse/documents/LU0864714000-factsheet.pdf</t>
+          <t>https://www.ethenea.com/FileHandler.ashx?path=/Documents/Factsheets/FS_LU0308864023_DE_MainFirst%20-%20Top%20European%20Ideas%20Fund%20(A).pdf</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://www.ethenea.com/de-de/mainfirst-absolute-return-multi-asset/</t>
+          <t>https://www.ethenea.com/de-de/_mainfirst-funds/mainfirst-top-european-ideas-fund/</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Factsheet ETHENEA (DE, part A, ISIN présent) au 27/02/2026 hébergée par finanzfluss : ANCIENNE (&gt;3 mois). Compartiment absorbé par LAIQON SICAV le 01/10/2026 (avis ETHENEA du 02/10/2026) ; plus de factsheet sur le site ETHENEA (404).</t>
+          <t>Gestion reprise par ETHENEA. Factsheets DE et EN datées 30/06/2026 seulement : ANCIENNE (&gt;3 mois), pas de version plus récente publiée sur le site.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LU0864709349</t>
+          <t>MT7000036042</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>MAINFIRST GLOBAL EQUITIES FUND A EUR</t>
+          <t>MFP GLOBAL SYSTEMATIC B EUR</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Mainfirst Affiliated Fund Managers S.A.</t>
+          <t>MFP Sicav p.l.c.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AUTRE_SOURCE</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>autre</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>27/02/2026</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
+          <t>INTROUVABLE</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>https://assets.finanzfluss.de/hippoverse/documents/LU0864709349-factsheet.pdf</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>https://www.ethenea.com/de-de/mainfirst-global-equities-fund/</t>
+          <t>non</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Factsheet ETHENEA (DE, part A, ISIN présent) au 27/02/2026 hébergée par finanzfluss : ANCIENNE (&gt;3 mois). Compartiment absorbé par LAIQON SICAV le 01/10/2026 (avis ETHENEA du 02/10/2026) ; plus de factsheet sur le site ETHENEA (404).</t>
+          <t>Aucun site gestionnaire joignable (MFP Sicav p.l.c., Malte; sous-gestionnaire Invest4Growth: domaines testés injoignables/refusés par le proxy). Absent de fundinfo (LU/BE/FR/CH/GB/IE/MT...). 2 WebSearch sans factsheet. Morningstar non testé faute d'URL documentaire publique.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LU1856130205</t>
+          <t>FR0000299356</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>MAINFIRST GLOBAL EQUITIES UNCONSTRAINED A EUR</t>
+          <t>NORDEN EUR</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mainfirst Affiliated Fund Managers S.A.</t>
+          <t>Lazard Frères Gestion</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>AUTRE_SOURCE</t>
+          <t>TROUVE</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>autre</t>
+          <t>gestionnaire</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>30/04/2025</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -27171,34 +27515,34 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>https://assets.finanzfluss.de/hippoverse/documents/LU1856130205-factsheet.pdf</t>
+          <t>https://www.lazardassetmanagement.com/docs/191104/FR0000299356_Factsheet_French%20(France).pdf</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.ethenea.com/de-de/mainfirst-global-equities-unconstrained-fund/</t>
+          <t>https://www.lazardfreresgestion.com/fr/fr_fr/fonds/fond-details/16/541.html</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Factsheet ETHENEA (DE, part A, ISIN présent) au 27/02/2026 hébergée par finanzfluss : ANCIENNE (&gt;3 mois). Compartiment absorbé par LAIQON SICAV le 01/10/2026 (avis ETHENEA du 02/10/2026) ; plus de factsheet sur le site ETHENEA (404).</t>
+          <t>TRÈS ANCIENNE (04-2025, mois seul) : fonds renommé Norden SRI ; la page fonds actuelle ne propose aucun reporting mensuel.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>LU2381585830</t>
+          <t>FR0013357704</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>MAINFIRST MEGATRENDS ASIA A USD</t>
+          <t>OMEGA ALLOCATION FLEXIBLE R EUR</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ETHENEA Independent Investors S.A.</t>
+          <t>Lazard Frères Gestion</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -27214,86 +27558,67 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>https://www.ethenea.com/en-lu/_mainfirst-funds/mainfirst-megatrends-asia/</t>
+          <t>https://www.lazardfreresgestion.com/fr/fr_fr/fonds/fond-details/16/6793.html</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Pas de factsheet sur la page ETHENEA (seulement KID/prospectus/avis); lien factsheetslive renvoie 'document non disponible'. Avis du 02/10/2026: fonds absorbé par LAIQON SICAV - Megatrends Asia au 01/10/2026 (fusion sur VNI du 30/09/2026).</t>
+          <t>FCP Omega Allocation Flexible (Lazard Frères Gestion, fonds dédié) : la page fonds ne publie que DIC, prospectus et rapports annuels/semestriels, aucun reporting mensuel ; Morningstar inaccessible (anti-bot).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LU0308864023</t>
+          <t>LU1417813323</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>MAINFIRST TOP EUROPEAN IDEAS A EUR</t>
+          <t>ORCADIA GLOBAL SUSTAINABLE BALANCED O EUR</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Mainfirst Affiliated Fund Managers S.A.</t>
+          <t>FundPartner Solutions (Europe) S.A.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>TROUVE</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>gestionnaire</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
+          <t>INTROUVABLE</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>https://www.ethenea.com/FileHandler.ashx?path=/Documents/Factsheets/FS_LU0308864023_DE_MainFirst%20-%20Top%20European%20Ideas%20Fund%20(A).pdf</t>
+          <t>non</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>https://www.ethenea.com/de-de/_mainfirst-funds/mainfirst-top-european-ideas-fund/</t>
+          <t>https://www.fundinfo.com/en/LU-priv/LandingPage?query=LU1417813323</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Gestion reprise par ETHENEA. Factsheets DE et EN datées 30/06/2026 seulement : ANCIENNE (&gt;3 mois), pas de version plus récente publiée sur le site.</t>
+          <t>Part confirmée sur fundinfo (Protea - Orcadia GSB O Acc) mais aucun reporting mensuel publié (seulement AR/SAR/KID/prospectus, toutes juridictions testées). Site du gestionnaire Orcadia (orcadia.ch / orcadia-am.*) inaccessible depuis l'environnement (proxy 502). Recherche web : seulement pages de données tierces (finanzen.ch).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MT7000036042</t>
+          <t>LU1171478784</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MFP GLOBAL SYSTEMATIC B EUR</t>
+          <t>QUEST CLEANTECH R EUR</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MFP Sicav p.l.c.</t>
+          <t>Selectum Vermogensbeheer NV</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -27309,77 +27634,57 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Aucun site gestionnaire joignable (MFP Sicav p.l.c., Malte; sous-gestionnaire Invest4Growth: domaines testés injoignables/refusés par le proxy). Absent de fundinfo (LU/BE/FR/CH/GB/IE/MT...). 2 WebSearch sans factsheet. Morningstar non testé faute d'URL documentaire publique.</t>
+          <t>Pas de factsheet : fundinfo n'a que AR/SAR/PR/PRIIP/EAR et des exports de scénarios KMS (pas une fiche) ; la page Quest Cleantech de capricorn.be (ancien gestionnaire) a disparu (dernier doc vu : portefeuille au 30/09/2025) ; rien sur selectum.be.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FR0010871830</t>
+          <t>FR0010283838</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MONETA LONG SHORT R EUR</t>
+          <t>ROCHE-BRUNE ZONE EURO ACTIONS P EUR</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Moneta Asset Management</t>
+          <t>ROCHE-BRUNE ASSET MANAGEMENT</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>AUTRE_SOURCE</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>autre</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>28/08/2026</t>
+          <t>INTROUVABLE</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>https://assets.finanzfluss.de/hippoverse/documents/FR0010871830-factsheet.pdf</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>https://www.moneta.fr/fonds/documents-a-telecharger</t>
+          <t>non</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Lettre mensuelle EN Moneta (Part R, ISIN présent) 'as of 28 August 2026', hébergée par finanzfluss. Site Moneta : bibliothèque derrière un login profil (TYPO3) non contournable en curl.</t>
+          <t>Roche-Brune AM absorbée par APICIL AM (fonds renommés en 2025) ; anciens domaines roche-brune.com injoignables ; site APICIL AM bloqué par Cloudflare (403) ; aucun reporting mensuel trouvé via recherche. | Passe fix : fundinfo (FR/LU/DE/CH/BE-priv) sans fiche mensuelle (MR) ; Morningstar LatestDoc type 52 : 404.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>LU0445386369</t>
+          <t>LU2228414459</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NORDEA 1 - ALPHA 10 MA BP EUR</t>
+          <t>SHELTER UCITS CORE SATELLITE FUND 60 IC EUR</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Nordea Investment Funds S.A.</t>
+          <t>SHELTER INVESTMENT MANAGEMENT</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -27393,26 +27698,31 @@
           <t>non</t>
         </is>
       </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>https://shelter-im.com/fr/onze-fondsen</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Site Nordea (nordea.lu) : pages fonds et documents servis dynamiquement par l'API Kurtosys (jeton requis, HTTP 401) ; noms de fichiers non devinables via /documents/ ; Morningstar bloqué (challenge anti-bot). Aucune factsheet téléchargée/vérifiée ; sources tierces (Standard Life, Finect) mentionnent des factsheets 2026 sans PDF officiel vérifié.</t>
+          <t>Site ShelteR IM : uniquement KID, prospectus, rapports annuels/semestriels, NAV et documents SFDR; aucune factsheet/reporting mensuel publié. Fichiers nommés '..._2026-02-27.pdf' vérifiés = KID, pas des factsheets. Recherche web : seules des factsheets Vivium (fonds d'assurance, autres ISIN, ≤31/12/2025). Morningstar non joignable (timeout).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>LU0602539602</t>
+          <t>LU2880650804</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NORDEA 1 - EMERGING STARS EQUITY FUND BP USD</t>
+          <t>SHELTER UCITS GARDANTO CORE FUND IC EUR</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nordea Investment Funds S.A.</t>
+          <t>SHELTER INVESTMENT MANAGEMENT</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -27426,26 +27736,31 @@
           <t>non</t>
         </is>
       </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>https://shelter-im.com/fr/onze-fondsen</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Site Nordea (nordea.lu) : pages fonds et documents servis dynamiquement par l'API Kurtosys (jeton requis, HTTP 401) ; noms de fichiers non devinables via /documents/ ; Morningstar bloqué (challenge anti-bot). Aucune factsheet téléchargée/vérifiée ; sources tierces (Standard Life, Finect) mentionnent des factsheets 2026 sans PDF officiel vérifié.</t>
+          <t>Site ShelteR IM : uniquement KID, prospectus, rapports annuels/semestriels, NAV et documents SFDR; aucune factsheet/reporting mensuel publié. Fichiers nommés '..._2026-02-27.pdf' vérifiés = KID, pas des factsheets. Recherche web : seules des factsheets Vivium (fonds d'assurance, autres ISIN, ≤31/12/2025). Morningstar non joignable (timeout).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>LU0348926287</t>
+          <t>LU2880681270</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NORDEA 1 - GLOBAL CLIMATE &amp; ENVIRONMENT BP EUR</t>
+          <t>SHELTER UCITS GARDANTO DYNAMIC FUND IC EUR</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Nordea Investment Funds S.A.</t>
+          <t>SHELTER INVESTMENT MANAGEMENT</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -27459,26 +27774,31 @@
           <t>non</t>
         </is>
       </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://shelter-im.com/fr/onze-fondsen</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Site Nordea (nordea.lu) : pages fonds et documents servis dynamiquement par l'API Kurtosys (jeton requis, HTTP 401) ; noms de fichiers non devinables via /documents/ ; Morningstar bloqué (challenge anti-bot). Aucune factsheet téléchargée/vérifiée ; sources tierces (Standard Life, Finect) mentionnent des factsheets 2026 sans PDF officiel vérifié.</t>
+          <t>Site ShelteR IM : uniquement KID, prospectus, rapports annuels/semestriels, NAV et documents SFDR; aucune factsheet/reporting mensuel publié. Fichiers nommés '..._2026-02-27.pdf' vérifiés = KID, pas des factsheets. Recherche web : seules des factsheets Vivium (fonds d'assurance, autres ISIN, ≤31/12/2025). Morningstar non joignable (timeout).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LU2463526074</t>
+          <t>LU0556665551</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NORDEA 1 - GLOBAL CLIMATE ENGAGEMENT FUND BP USD</t>
+          <t>SMART VALUE INVESTORS EQUITY FLEXIBLE A EUR</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Nordea Investment Funds S.A.</t>
+          <t>Conventum Asset Management S.A.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -27492,26 +27812,31 @@
           <t>non</t>
         </is>
       </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>https://www.conventum.lu/en/bank/cam/fund-data-and-factsheets</t>
+        </is>
+      </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Site Nordea (nordea.lu) : pages fonds et documents servis dynamiquement par l'API Kurtosys (jeton requis, HTTP 401) ; noms de fichiers non devinables via /documents/ ; Morningstar bloqué (challenge anti-bot). Aucune factsheet téléchargée/vérifiée ; sources tierces (Standard Life, Finect) mentionnent des factsheets 2026 sans PDF officiel vérifié.</t>
+          <t>Docs du fonds sur la bibliothèque Fundsquare de Conventum (initiateur BLI) : seulement prospectus, rapports annuels/semestriels et KID (01/2026), pas de factsheet ; rien dans fundinfo ; recherche web sans factsheet.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LU0078812822</t>
+          <t>LU0407238897</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NORDEA 1 - NORWEGIAN SHRT-TERM BD BP NOK</t>
+          <t>SMART VALUE INVESTORS PATRIMOINE FLEXIBLE A EUR</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Nordea Investment Funds S.A.</t>
+          <t>Conventum Asset Management S.A.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -27525,26 +27850,31 @@
           <t>non</t>
         </is>
       </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>https://www.conventum.lu/en/bank/cam/fund-data-and-factsheets</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Site Nordea (nordea.lu) : pages fonds et documents servis dynamiquement par l'API Kurtosys (jeton requis, HTTP 401) ; noms de fichiers non devinables via /documents/ ; Morningstar bloqué (challenge anti-bot). Aucune factsheet téléchargée/vérifiée ; sources tierces (Standard Life, Finect) mentionnent des factsheets 2026 sans PDF officiel vérifié.</t>
+          <t>Docs du fonds sur la bibliothèque Fundsquare de Conventum (initiateur BLI) : seulement prospectus, rapports annuels/semestriels et KID (01/2026), pas de factsheet ; rien dans fundinfo ; recherche web sans factsheet.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>LU0227384020</t>
+          <t>BE6291427076</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NORDEA 1 - STABLE RETURN BP EUR</t>
+          <t>SPM GLOBAL FLEXIBLE Y EUR</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Nordea Investment Funds S.A.</t>
+          <t>Montségur</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -27558,31 +27888,26 @@
           <t>non</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>https://www.nordea.lu/en/professional/fund/stable-return-fund/</t>
-        </is>
-      </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Site Nordea (nordea.lu) : pages fonds et documents servis dynamiquement par l'API Kurtosys (jeton requis, HTTP 401) ; noms de fichiers non devinables via /documents/ ; Morningstar bloqué (challenge anti-bot). Aucune factsheet téléchargée/vérifiée ; sources tierces (Standard Life, Finect) mentionnent des factsheets 2026 sans PDF officiel vérifié.</t>
+          <t>Aucun résultat web pour l'ISIN ni le nom ; site Montségur Finance inaccessible (erreur proxy 502) ; Morningstar bloqué.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>LU3076185084</t>
+          <t>FR0000016172</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NORDEA 1 EMPOWER EUROPE BP EUR</t>
+          <t>STRATEGIE RENDEMENT P EUR</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Nordea Investment Funds S.A.</t>
+          <t>APICIL ASSET MANAGEMENT</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -27596,31 +27921,26 @@
           <t>non</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>https://www.nordea.lu/en/professional/fund/empower-europe-fund/</t>
-        </is>
-      </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Site Nordea (nordea.lu) : pages fonds et documents servis dynamiquement par l'API Kurtosys (jeton requis, HTTP 401) ; noms de fichiers non devinables via /documents/ ; Morningstar bloqué (challenge anti-bot). Aucune factsheet téléchargée/vérifiée ; sources tierces (Standard Life, Finect) mentionnent des factsheets 2026 sans PDF officiel vérifié.</t>
+          <t>Site APICIL AM (apicil-asset-management.com) entièrement derrière un challenge Cloudflare (403, y compris sitemaps/uploads) ; aucune URL de reporting mensuel trouvée via recherche ; agrégateurs (epargnoo) : seulement le DIC. | Passe fix : fundinfo (FR/LU/DE/CH/BE-priv) sans fiche mensuelle (MR) ; Morningstar LatestDoc type 52 : 404.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LU0112467450</t>
+          <t>FR0010237503</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NORDEA 1 GLOBAL STABLE EQUITY BP EUR</t>
+          <t>STRATEGIE SOUVERAINETE EUROPEENNE P EUR</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Nordea Investment Funds S.A.</t>
+          <t>APICIL ASSET MANAGEMENT</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -27634,126 +27954,116 @@
           <t>non</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>https://www.nordea.lu/en/professional/fund/global-stable-equities/</t>
-        </is>
-      </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Site Nordea (nordea.lu) : pages fonds et documents servis dynamiquement par l'API Kurtosys (jeton requis, HTTP 401) ; noms de fichiers non devinables via /documents/ ; Morningstar bloqué (challenge anti-bot). Aucune factsheet téléchargée/vérifiée ; sources tierces (Standard Life, Finect) mentionnent des factsheets 2026 sans PDF officiel vérifié.</t>
+          <t>Site APICIL AM (apicil-asset-management.com) entièrement derrière un challenge Cloudflare (403, y compris sitemaps/uploads) ; aucune URL de reporting mensuel trouvée via recherche ; agrégateurs (epargnoo) : seulement le DIC. | Passe fix : fundinfo (FR/LU/DE/CH/BE-priv) sans fiche mensuelle (MR) ; Morningstar LatestDoc type 52 : 404.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FR0000299356</t>
+          <t>IE00BF2F6B09</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NORDEN EUR</t>
+          <t>TC NEW HORIZON GLOBAL BALANCED FUND C EUR</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Lazard Frères Gestion</t>
+          <t>Treasury Capital Fund Solutions</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>TROUVE</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>gestionnaire</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>30/04/2025</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
+          <t>INTROUVABLE</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>oui</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>https://www.lazardassetmanagement.com/docs/191104/FR0000299356_Factsheet_French%20(France).pdf</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>https://www.lazardfreresgestion.com/fr/fr_fr/fonds/fond-details/16/541.html</t>
+          <t>non</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>TRÈS ANCIENNE (04-2025, mois seul) : fonds renommé Norden SRI ; la page fonds actuelle ne propose aucun reporting mensuel.</t>
+          <t>Aucun site gestionnaire joignable (treasurycapital.ie / tcfundsolutions.com : échec de connexion) ; recherche web : uniquement agrégateurs (finanzen.ch/.at, part C EUR Acc, administrateur Gateway Fund Services). Morningstar SecId F000010EJL trouvé mais pages Morningstar bloquées (anti-bot) ; Finect n'a pas de document. | Passe fix : fundinfo (FR/LU/DE/CH/BE-priv) sans fiche mensuelle (MR) ; Morningstar LatestDoc type 52 : 404.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FR0013357704</t>
+          <t>LU2638914734</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>OMEGA ALLOCATION FLEXIBLE R EUR</t>
+          <t>TOBAM GLOBAL BLOCKCHAIN EQUITY FUND B2 EUR</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Lazard Frères Gestion</t>
+          <t>TOBAM</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>INTROUVABLE</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
+          <t>NON_VERIFIE</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>gestionnaire</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>30/12/2025</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>https://www.tobam.fr/wp-content/uploads/2025/12/TOBAM-Global-Blockchain-Equity-Factsheet-202512.pdf</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>https://www.lazardfreresgestion.com/fr/fr_fr/fonds/fond-details/16/6793.html</t>
+          <t>https://www.tobam.fr/%e2%82%bftobam-crypto-asset/tobam-global-blockchain-equity-fund/</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>FCP Omega Allocation Flexible (Lazard Frères Gestion, fonds dédié) : la page fonds ne publie que DIC, prospectus et rapports annuels/semestriels, aucun reporting mensuel ; Morningstar inaccessible (anti-bot).</t>
+          <t>Seule factsheet sur le site : 'TOBAM Global Blockchain Equity Strategy' du 30/12/2025, sans ISIN ni part B2 identifiée ; ANCIENNE (&gt;3 mois). Les documents de la part B2 listés sur la page (KID, prospectus, rapports) ne comprennent pas de reporting mensuel. Morningstar : aucun.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>LU1417813323</t>
+          <t>FR0007072160</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ORCADIA GLOBAL SUSTAINABLE BALANCED O EUR</t>
+          <t>TRUSTEAM OPTIMUM A EUR</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>FundPartner Solutions (Europe) S.A.</t>
+          <t>TrusTeam Finance</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -27767,36 +28077,41 @@
           <t>non</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>https://www.fundinfo.com/en/LU-priv/LandingPage?query=LU1417813323</t>
-        </is>
-      </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Part confirmée sur fundinfo (Protea - Orcadia GSB O Acc) mais aucun reporting mensuel publié (seulement AR/SAR/KID/prospectus, toutes juridictions testées). Site du gestionnaire Orcadia (orcadia.ch / orcadia-am.*) inaccessible depuis l'environnement (proxy 502). Recherche web : seulement pages de données tierces (finanzen.ch).</t>
+          <t>trusteam.fr ne résout plus (DNS); KID d'oct. 2025 indique transfert de gestion à Auris Gestion (aurisgestion.com, espace réservé, aucune page fonds accessible); Morningstar (F0GBR04IQI) 404.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>LU1171478784</t>
+          <t>LU0558384706</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>QUEST CLEANTECH R EUR</t>
+          <t>VECTOR FLEXIBLE C3 EUR</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Selectum Vermogensbeheer NV</t>
+          <t>Vector Asset Management S.A.</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>INTROUVABLE</t>
+          <t>NON_VERIFIE</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>gestionnaire</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -27805,31 +28120,51 @@
           <t>non</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>https://www.vector.lu/mediastorage/FSDocument/A0/1279/factsheet-flexible-202608-new.pdf</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>https://www.vector.lu/en/fund/flexible/</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Pas de factsheet : fundinfo n'a que AR/SAR/PR/PRIIP/EAR et des exports de scénarios KMS (pas une fiche) ; la page Quest Cleantech de capricorn.be (ancien gestionnaire) a disparu (dernier doc vu : portefeuille au 30/09/2025) ; rien sur selectum.be.</t>
+          <t>Seule factsheet publiée : niveau compartiment Vector Flexible (août 2026, as of 31/08/2026) couvrant les parts C1, P, I1 ; part C3 (LU0558384706) ni nommée ni ISIN présent. Aucune factsheet C3 (gestionnaire ; Morningstar renvoie un document 2014 erroné).</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FR0010283838</t>
+          <t>LU0366797354</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ROCHE-BRUNE ZONE EURO ACTIONS P EUR</t>
+          <t>VECTOR NAVIGATOR C3 EUR</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ROCHE-BRUNE ASSET MANAGEMENT</t>
+          <t>Vector Asset Management S.A.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>INTROUVABLE</t>
+          <t>NON_VERIFIE</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>gestionnaire</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -27838,26 +28173,36 @@
           <t>non</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>https://www.vector.lu/mediastorage/FSDocument/A0/1280/factsheet-navigator-202608-new.pdf</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>https://www.vector.lu/en/fund/navigator/</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Roche-Brune AM absorbée par APICIL AM (fonds renommés en 2025) ; anciens domaines roche-brune.com injoignables ; site APICIL AM bloqué par Cloudflare (403) ; aucun reporting mensuel trouvé via recherche.</t>
+          <t>Seule factsheet publiée : niveau compartiment Vector Navigator (août 2026, as of 31/08/2026) couvrant C1, P, I1 ; part C3 (LU0366797354) absente. Aucune factsheet C3 trouvée.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>LU2228414459</t>
+          <t>LU1496475119</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SHELTER UCITS CORE SATELLITE FUND 60 IC EUR</t>
+          <t>WATERLOO GLOBAL FLEXIBLE R EUR</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SHELTER INVESTMENT MANAGEMENT</t>
+          <t>Altum Management Company (Luxembourg) S.A.</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -27873,530 +28218,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>https://shelter-im.com/fr/onze-fondsen</t>
+          <t>https://www.waterloo-am.com/documents</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Site ShelteR IM : uniquement KID, prospectus, rapports annuels/semestriels, NAV et documents SFDR; aucune factsheet/reporting mensuel publié. Fichiers nommés '..._2026-02-27.pdf' vérifiés = KID, pas des factsheets. Recherche web : seules des factsheets Vivium (fonds d'assurance, autres ISIN, ≤31/12/2025). Morningstar non joignable (timeout).</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>LU2880650804</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>SHELTER UCITS GARDANTO CORE FUND IC EUR</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>SHELTER INVESTMENT MANAGEMENT</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>INTROUVABLE</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>https://shelter-im.com/fr/onze-fondsen</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Site ShelteR IM : uniquement KID, prospectus, rapports annuels/semestriels, NAV et documents SFDR; aucune factsheet/reporting mensuel publié. Fichiers nommés '..._2026-02-27.pdf' vérifiés = KID, pas des factsheets. Recherche web : seules des factsheets Vivium (fonds d'assurance, autres ISIN, ≤31/12/2025). Morningstar non joignable (timeout).</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>LU2880681270</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>SHELTER UCITS GARDANTO DYNAMIC FUND IC EUR</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>SHELTER INVESTMENT MANAGEMENT</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>INTROUVABLE</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>https://shelter-im.com/fr/onze-fondsen</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Site ShelteR IM : uniquement KID, prospectus, rapports annuels/semestriels, NAV et documents SFDR; aucune factsheet/reporting mensuel publié. Fichiers nommés '..._2026-02-27.pdf' vérifiés = KID, pas des factsheets. Recherche web : seules des factsheets Vivium (fonds d'assurance, autres ISIN, ≤31/12/2025). Morningstar non joignable (timeout).</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>LU0556665551</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>SMART VALUE INVESTORS EQUITY FLEXIBLE A EUR</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Conventum Asset Management S.A.</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>INTROUVABLE</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>https://www.conventum.lu/en/bank/cam/fund-data-and-factsheets</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Docs du fonds sur la bibliothèque Fundsquare de Conventum (initiateur BLI) : seulement prospectus, rapports annuels/semestriels et KID (01/2026), pas de factsheet ; rien dans fundinfo ; recherche web sans factsheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>LU0407238897</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>SMART VALUE INVESTORS PATRIMOINE FLEXIBLE A EUR</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Conventum Asset Management S.A.</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>INTROUVABLE</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>https://www.conventum.lu/en/bank/cam/fund-data-and-factsheets</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Docs du fonds sur la bibliothèque Fundsquare de Conventum (initiateur BLI) : seulement prospectus, rapports annuels/semestriels et KID (01/2026), pas de factsheet ; rien dans fundinfo ; recherche web sans factsheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>BE6291427076</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>SPM GLOBAL FLEXIBLE Y EUR</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Montségur</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>INTROUVABLE</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Aucun résultat web pour l'ISIN ni le nom ; site Montségur Finance inaccessible (erreur proxy 502) ; Morningstar bloqué.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>FR0000016172</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>STRATEGIE RENDEMENT P EUR</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>APICIL ASSET MANAGEMENT</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>INTROUVABLE</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Site APICIL AM (apicil-asset-management.com) entièrement derrière un challenge Cloudflare (403, y compris sitemaps/uploads) ; aucune URL de reporting mensuel trouvée via recherche ; agrégateurs (epargnoo) : seulement le DIC.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>FR0010237503</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>STRATEGIE SOUVERAINETE EUROPEENNE P EUR</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>APICIL ASSET MANAGEMENT</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>INTROUVABLE</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Site APICIL AM (apicil-asset-management.com) entièrement derrière un challenge Cloudflare (403, y compris sitemaps/uploads) ; aucune URL de reporting mensuel trouvée via recherche ; agrégateurs (epargnoo) : seulement le DIC.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>IE00BF2F6B09</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>TC NEW HORIZON GLOBAL BALANCED FUND C EUR</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Treasury Capital Fund Solutions</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>INTROUVABLE</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>Aucun site gestionnaire joignable (treasurycapital.ie / tcfundsolutions.com : échec de connexion) ; recherche web : uniquement agrégateurs (finanzen.ch/.at, part C EUR Acc, administrateur Gateway Fund Services). Morningstar SecId F000010EJL trouvé mais pages Morningstar bloquées (anti-bot) ; Finect n'a pas de document.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>LU2638914734</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>TOBAM GLOBAL BLOCKCHAIN EQUITY FUND B2 EUR</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>TOBAM</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>NON_VERIFIE</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>gestionnaire</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>30/12/2025</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>OUI</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>https://www.tobam.fr/wp-content/uploads/2025/12/TOBAM-Global-Blockchain-Equity-Factsheet-202512.pdf</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>https://www.tobam.fr/%e2%82%bftobam-crypto-asset/tobam-global-blockchain-equity-fund/</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Seule factsheet sur le site : 'TOBAM Global Blockchain Equity Strategy' du 30/12/2025, sans ISIN ni part B2 identifiée ; ANCIENNE (&gt;3 mois). Les documents de la part B2 listés sur la page (KID, prospectus, rapports) ne comprennent pas de reporting mensuel. Morningstar : aucun.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>FR0007072160</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>TRUSTEAM OPTIMUM A EUR</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>TrusTeam Finance</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>INTROUVABLE</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>trusteam.fr ne résout plus (DNS); KID d'oct. 2025 indique transfert de gestion à Auris Gestion (aurisgestion.com, espace réservé, aucune page fonds accessible); Morningstar (F0GBR04IQI) 404.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>LU0558384706</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>VECTOR FLEXIBLE C3 EUR</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Vector Asset Management S.A.</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>NON_VERIFIE</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>gestionnaire</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>https://www.vector.lu/mediastorage/FSDocument/A0/1279/factsheet-flexible-202608-new.pdf</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>https://www.vector.lu/en/fund/flexible/</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>Seule factsheet publiée : niveau compartiment Vector Flexible (août 2026, as of 31/08/2026) couvrant les parts C1, P, I1 ; part C3 (LU0558384706) ni nommée ni ISIN présent. Aucune factsheet C3 (gestionnaire ; Morningstar renvoie un document 2014 erroné).</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>LU0366797354</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>VECTOR NAVIGATOR C3 EUR</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Vector Asset Management S.A.</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>NON_VERIFIE</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>gestionnaire</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>https://www.vector.lu/mediastorage/FSDocument/A0/1280/factsheet-navigator-202608-new.pdf</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>https://www.vector.lu/en/fund/navigator/</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Seule factsheet publiée : niveau compartiment Vector Navigator (août 2026, as of 31/08/2026) couvrant C1, P, I1 ; part C3 (LU0366797354) absente. Aucune factsheet C3 trouvée.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>LU1496475119</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>WATERLOO GLOBAL FLEXIBLE R EUR</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Altum Management Company (Luxembourg) S.A.</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>INTROUVABLE</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>https://www.waterloo-am.com/documents</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>Waterloo Global Flexible R EUR (Waterloo Sicav, gérant Waterloo AM). Section SICAVs du site waterloo-am.com protégée par mot de passe ; fundinfo ne publie que prospectus (2024) et rapport semestriel (30/06/2024), aucune fiche mensuelle ; WebSearch sans résultat. Site Altum injoignable.</t>
+          <t>Waterloo Global Flexible R EUR (Waterloo Sicav, gérant Waterloo AM). Section SICAVs du site waterloo-am.com protégée par mot de passe ; fundinfo ne publie que prospectus (2024) et rapport semestriel (30/06/2024), aucune fiche mensuelle ; WebSearch sans résultat. Site Altum injoignable. | Passe fix : fundinfo (FR/LU/DE/CH/BE-priv) sans fiche mensuelle (MR) ; Morningstar LatestDoc type 52 : 404. (SecId F00000XYNC)</t>
         </is>
       </c>
     </row>
